--- a/04_Excel_Workbook/Naukri_Saaf_Executive_Analytics_v4.xlsx
+++ b/04_Excel_Workbook/Naukri_Saaf_Executive_Analytics_v4.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform Benchmark" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requisition Survival" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listing Age Analysis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High-Risk Listings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -573,7 +573,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>AVG GHOST LIFESPAN</t>
+          <t>OVERALL MEAN AGE</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
         <v>0.3998596983514556</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>110.2897196261682</v>
+        <v>32.71623991581901</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0.8309365135040336</v>
@@ -656,7 +656,7 @@
         <v>0.6001403016485444</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>5.834015195791935</v>
+        <v>5.828170660432495</v>
       </c>
     </row>
     <row r="11">
@@ -677,7 +677,7 @@
         <v>0.2497369344089793</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>50.68539325842696</v>
+        <v>53.41853932584269</v>
       </c>
     </row>
     <row r="12">
@@ -698,7 +698,7 @@
         <v>0.1501227639424763</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>110.2897196261682</v>
+        <v>105.7663551401869</v>
       </c>
     </row>
   </sheetData>
@@ -721,7 +721,7 @@
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -771,10 +771,10 @@
         <v>873</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>356</v>
+        <v>322</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.4077892325315006</v>
+        <v>0.3688430698739977</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>63.8</v>
@@ -790,10 +790,10 @@
         <v>978</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.02658486707566462</v>
+        <v>0.05214723926380368</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0.3</v>
@@ -809,10 +809,10 @@
         <v>1000</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>37.2</v>
@@ -832,20 +832,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="69" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KAPLAN-MEIER REQUISITION HALF-LIFE DYNAMICS</t>
+          <t>CROSS-SECTIONAL LISTING AGE DISTRIBUTION (SNAPSHOT AT SCRAPE TIME)</t>
         </is>
       </c>
     </row>
@@ -864,81 +868,137 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>Sample Size</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Mean Days Live</t>
+          <t>Mean Days</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>Median Half-Life (Days)</t>
+          <t>Median Days</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>P25 Days</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>P75 Days</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>P90 Days</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Max Days</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Ghost Status</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Genuine</t>
+          <t>All Listings</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>1711</v>
+        <v>2851</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>6.3</v>
+        <v>32.7</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>365</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Ghost Status</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Suspect</t>
+          <t>Glassdoor</t>
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>712</v>
+        <v>873</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>46.3</v>
+        <v>63.8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>31</v>
+        <v>41</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>Ghost Status</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Ghost</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>428</v>
+        <v>978</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>96.2</v>
+        <v>0.3</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>128</v>
+        <v>0</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -956,99 +1016,60 @@
         <v>1000</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>30</v>
+        <v>37.2</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>12</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>365</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Salary Disclosure</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Salary Hidden/Missing</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>978</v>
+        <v>2851</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1.2</v>
+        <v>32.7</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Glassdoor</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>873</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Salary Disclosure</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Disclosed</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>482</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Salary Disclosure</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Undisclosed</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>2369</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A1:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1065,7 +1086,7 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="75" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -1118,17 +1139,17 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>GD1007989727669</t>
+          <t>GD1010075318368</t>
         </is>
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Process Analyst- Six sigma - Bangalore</t>
         </is>
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>Hyperthink Systems</t>
+          <t>Medi Assist Insurance TPA Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
@@ -1137,7 +1158,7 @@
         </is>
       </c>
       <c r="E2" s="10" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>1</v>
@@ -1156,17 +1177,17 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>GD1009929896784</t>
+          <t>GD1009991584703</t>
         </is>
       </c>
       <c r="B3" s="19" t="inlineStr">
         <is>
-          <t>Specialist - Data Analyst (Main Converter)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>Nordex SE</t>
+          <t>BestPeers Infosystem Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
@@ -1175,7 +1196,7 @@
         </is>
       </c>
       <c r="E3" s="10" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>1</v>
@@ -1194,17 +1215,17 @@
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>GD1007838294703</t>
+          <t>GD1009422806620</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst (ETL Tools)</t>
+          <t>Sr. Power Bi Developer</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>Alpha Analytics Services Private Limited</t>
+          <t>TechTree IT Systems Pvt Ltd.</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
@@ -1213,7 +1234,7 @@
         </is>
       </c>
       <c r="E4" s="10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>1</v>
@@ -1225,24 +1246,24 @@
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>GD1010054187264</t>
+          <t>GD1009424315122</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>Indium Software Inc.</t>
+          <t>Equiniti</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -1251,7 +1272,7 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>1</v>
@@ -1270,17 +1291,17 @@
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>GD1008297385561</t>
+          <t>GD1009929896784</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Jr./ Sr. Machine Learning Developer</t>
+          <t>Specialist - Data Analyst (Main Converter)</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>Vertscend Automation Pvt Ltd</t>
+          <t>Nordex SE</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
@@ -1289,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>1</v>
@@ -1308,17 +1329,17 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>GD1009801880286</t>
+          <t>GD1009784661520</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Data Scientist – R01551326</t>
+          <t>Data Analyst / Biostatistician</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>Brillio</t>
+          <t>Rehoboth Academic Services</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -1346,17 +1367,17 @@
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>GD1010037476315</t>
+          <t>GD1009937947571</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>InOpTra Digital Pvt Ltd</t>
+          <t>Mettler-Toledo International Inc.</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -1365,7 +1386,7 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>1</v>
@@ -1384,17 +1405,17 @@
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>GD1010015131663</t>
+          <t>GD1008011539630</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Software Engineer-Frontend</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>Rocketlane Corp</t>
+          <t>Ideapoke Technologies Pvt. Ltd</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -1403,7 +1424,7 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>1</v>
@@ -1422,17 +1443,17 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>GD1009937947571</t>
+          <t>GD1007758833254</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>Mettler-Toledo International Inc.</t>
+          <t>Zumen Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -1441,7 +1462,7 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>1</v>
@@ -1460,17 +1481,17 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>GD1009824167819</t>
+          <t>GD1009422177997</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Front-end Developer</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Riverstone Info Tech</t>
+          <t>Hack2skill Private Limited</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -1479,7 +1500,7 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>1</v>
@@ -1498,17 +1519,17 @@
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>GD1005863473199</t>
+          <t>GD1007301187953</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - SDE I</t>
+          <t>Front-end Engineer</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>Pinnacle Consultz</t>
+          <t>PaGaLGuY</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -1517,7 +1538,7 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>1</v>
@@ -1536,17 +1557,17 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>GD1009829066350</t>
+          <t>GD1007767972502</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Opening For Data Analyst</t>
+          <t>Web Application Developer</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Sunshine Manpower Solution &amp; Services</t>
+          <t>Allies Interactive</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -1555,7 +1576,7 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>1</v>
@@ -1574,17 +1595,17 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>GD1009824167887</t>
+          <t>GD1007972739731</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Data Analytics</t>
+          <t>React Lead Developer</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>Riverstone Info Tech</t>
+          <t xml:space="preserve">Appzia Technologies Pte. Ltd. </t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -1593,7 +1614,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>1</v>
@@ -1612,17 +1633,17 @@
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>GD1009211007543</t>
+          <t>GD1009790591797</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wonder Home Finance Ltd </t>
+          <t>United Parcel Service, Inc.</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -1650,17 +1671,17 @@
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>GD1009422177997</t>
+          <t>GD1009686139823</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Front-end Developer</t>
+          <t>Front End Engineer</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>Hack2skill Private Limited</t>
+          <t xml:space="preserve">Eastern Book Co. (P) Ltd. </t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
@@ -1669,7 +1690,7 @@
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>1</v>
@@ -1688,17 +1709,17 @@
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>GD1007582396429</t>
+          <t>GD1008506603359</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>React Js Developer</t>
+          <t>Web Developer - Senior</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>NeuraTech Pvt Ltd</t>
+          <t xml:space="preserve">Meriton Group </t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -1726,17 +1747,17 @@
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>GD1007972739731</t>
+          <t>GD1010017223414</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>React Lead Developer</t>
+          <t>Computer Vision Engineer</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Appzia Technologies Pte. Ltd. </t>
+          <t>Infolks Pvt Ltd</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -1745,7 +1766,7 @@
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>1</v>
@@ -1757,24 +1778,24 @@
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>GD1005649563038</t>
+          <t>GD1008910208262</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>WEB DEVELOPER</t>
+          <t>React JS &amp; Next JS Developer</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>B2L Mobitech pvt Ltd</t>
+          <t>Aadrika Enterprises</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -1783,7 +1804,7 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>130</v>
+        <v>365</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>1</v>
@@ -1802,17 +1823,17 @@
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>GD1010012156119</t>
+          <t>GD1009625976564</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>ML Engineer – Databricks</t>
+          <t>Front End UI Developer July 2026 Sector 6, Noida</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>InfoTrellis</t>
+          <t>DigiVersal Consultant Pvt Ltd</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -1821,7 +1842,7 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>1</v>
@@ -1840,17 +1861,17 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>GD1008952246347</t>
+          <t>GD1009606712806</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>RocketTEch</t>
+          <t>LogicHive Solutions Pvt Ltd</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -1859,7 +1880,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>133</v>
+        <v>365</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>1</v>
@@ -1878,17 +1899,17 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>GD1006041114241</t>
+          <t>GD1009605810137</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer-ReactJS/AngularJS</t>
+          <t>SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>Nuchange Informatics</t>
+          <t>PayCraft Solutions Pvt. Ltd</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
@@ -1897,7 +1918,7 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>1</v>
@@ -1916,17 +1937,17 @@
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>GD1007758833254</t>
+          <t>GD1009906961196</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>AI/ML &amp; Data Engineer</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>Zumen Technologies Pvt Ltd</t>
+          <t>Congruent Info-Tech Pvt. Ltd</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -1935,7 +1956,7 @@
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>1</v>
@@ -1954,17 +1975,17 @@
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>GD1008506603359</t>
+          <t>GD1009790591402</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Web Developer - Senior</t>
+          <t>Data Scientist- Pytorch/ TensorFlow</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meriton Group </t>
+          <t>United Parcel Service, Inc.</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
@@ -1973,7 +1994,7 @@
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>1</v>
@@ -1992,17 +2013,17 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>GD1007954581337</t>
+          <t>GD1009834334893</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>React Js Developer</t>
+          <t>REACT JS FRONT END DEVELOPER</t>
         </is>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>Brown Button Private Limited</t>
+          <t>SKC Infotech</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -2030,17 +2051,17 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>GD1010017223414</t>
+          <t>GD1007754610218</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>Computer Vision Engineer</t>
+          <t>JavaScript Frontend Developer</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>Infolks Pvt Ltd</t>
+          <t>DesignnBuy Pvt Ltd</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
@@ -2049,7 +2070,7 @@
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>1</v>
@@ -2068,17 +2089,17 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>GD1009790591402</t>
+          <t>GD1008233108435</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>Data Scientist- Pytorch/ TensorFlow</t>
+          <t>Back-end Developer</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>United Parcel Service, Inc.</t>
+          <t>Riaxe Systems</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -2087,7 +2108,7 @@
         </is>
       </c>
       <c r="E27" s="10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>1</v>
@@ -2106,17 +2127,17 @@
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>GD1009906961196</t>
+          <t>GD1009704436666</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>AI/ML &amp; Data Engineer</t>
+          <t>Software Engineer -JAVA</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>Congruent Info-Tech Pvt. Ltd</t>
+          <t>Kizora Software Private Limited</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
@@ -2125,7 +2146,7 @@
         </is>
       </c>
       <c r="E28" s="10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>1</v>
@@ -2144,17 +2165,17 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>GD1009625976564</t>
+          <t>GD1008729660592</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>Front End UI Developer July 2026 Sector 6, Noida</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>DigiVersal Consultant Pvt Ltd</t>
+          <t>Osource Global Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -2182,17 +2203,17 @@
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>GD1007935453441</t>
+          <t>GD1009801880286</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Data Scientist – R01551326</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>E2M Solutions Pvt. Ltd.</t>
+          <t>Brillio</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
@@ -2201,7 +2222,7 @@
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>1</v>
@@ -2220,17 +2241,17 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>GD1008729660592</t>
+          <t>GD1009824167819</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>Osource Global Pvt. Ltd.</t>
+          <t>Riverstone Info Tech</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
@@ -2239,7 +2260,7 @@
         </is>
       </c>
       <c r="E31" s="10" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>1</v>
@@ -2258,17 +2279,17 @@
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>GD1009834334893</t>
+          <t>GD1009829066350</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>REACT JS FRONT END DEVELOPER</t>
+          <t>Opening For Data Analyst</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>SKC Infotech</t>
+          <t>Sunshine Manpower Solution &amp; Services</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
@@ -2277,7 +2298,7 @@
         </is>
       </c>
       <c r="E32" s="10" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>1</v>
@@ -2296,17 +2317,17 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>GD1009227091208</t>
+          <t>GD1010015131663</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Software Engineer-Frontend</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>ekZero Corporation</t>
+          <t>Rocketlane Corp</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
@@ -2315,7 +2336,7 @@
         </is>
       </c>
       <c r="E33" s="10" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>1</v>
@@ -2334,17 +2355,17 @@
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>GD1009960227232</t>
+          <t>GD1010067307304</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>React JS Developer</t>
+          <t>Jr. Frontend Developer</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>HorizonCore InfoSoft Pvt. Ltd.</t>
+          <t>Enzigma Software Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
@@ -2353,7 +2374,7 @@
         </is>
       </c>
       <c r="E34" s="10" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="F34" s="11" t="n">
         <v>1</v>
@@ -2372,17 +2393,17 @@
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>GD1010057039510</t>
+          <t>GD1006549799475</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>Engineer, Staff - IEIOT AI Systems</t>
+          <t>ReactJS Developers</t>
         </is>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>Qualcomm Incorporated</t>
+          <t xml:space="preserve">Salus Technologies Pvt Ltd </t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
@@ -2391,7 +2412,7 @@
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>1</v>
@@ -2410,12 +2431,12 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>GD1010012156135</t>
+          <t>GD1010012156119</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>ML Engineer – Snowflake</t>
+          <t>ML Engineer – Databricks</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
@@ -2448,17 +2469,17 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>GD1007219199125</t>
+          <t>GD1010012156135</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>UI Developer</t>
+          <t>ML Engineer – Snowflake</t>
         </is>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>Blue Horizon Infotech</t>
+          <t>InfoTrellis</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -2467,7 +2488,7 @@
         </is>
       </c>
       <c r="E37" s="10" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>1</v>
@@ -2486,17 +2507,17 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>GD1007767972502</t>
+          <t>GD1010057179983</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>Web Application Developer</t>
+          <t>AI/ML Engineers</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>Allies Interactive</t>
+          <t>Broadridge Financial Solutions, Inc.</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -2505,7 +2526,7 @@
         </is>
       </c>
       <c r="E38" s="10" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>1</v>
@@ -2524,17 +2545,17 @@
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>GD1007301187953</t>
+          <t>GD1009563892630</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>Front-end Engineer</t>
+          <t>ReactJS developer</t>
         </is>
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>PaGaLGuY</t>
+          <t xml:space="preserve">Netfillip Technologies Private Limited </t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
@@ -2562,17 +2583,17 @@
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>GD1009235618698</t>
+          <t>GD1009433735056</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>Softura Inc.</t>
+          <t>Awapal Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -2584,7 +2605,7 @@
         <v>137</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -2600,17 +2621,17 @@
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>GD1010170069400</t>
+          <t>GD1009065281506</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Front End Developer</t>
         </is>
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finastra </t>
+          <t>Codeclouds IT Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -2619,10 +2640,10 @@
         </is>
       </c>
       <c r="E41" s="10" t="n">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -2638,17 +2659,17 @@
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>GD1010150210469</t>
+          <t>GD1007582396429</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>React Js Developer</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>Blackbuck Insights, LLC</t>
+          <t>NeuraTech Pvt Ltd</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -2657,10 +2678,10 @@
         </is>
       </c>
       <c r="E42" s="10" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -2676,17 +2697,17 @@
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>GD1006367490721</t>
+          <t>GD1006649775121</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Frontend Developer (Angular, JavaScript, Lighthouse Performance Testing)</t>
         </is>
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>Govche India Private Limited</t>
+          <t>Mobile Programming LLC</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -2698,7 +2719,7 @@
         <v>130</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -2714,17 +2735,17 @@
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>GD1008910208262</t>
+          <t>GD1007467247069</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>React JS &amp; Next JS Developer</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>Aadrika Enterprises</t>
+          <t>Rrayze Business Solutions</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -2733,10 +2754,10 @@
         </is>
       </c>
       <c r="E44" s="10" t="n">
-        <v>365</v>
+        <v>130</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -2752,17 +2773,17 @@
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>GD1006549799475</t>
+          <t>GD1009724595329</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>ReactJS Developers</t>
+          <t>Sr Frontend Engineer</t>
         </is>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Salus Technologies Pvt Ltd </t>
+          <t>Excel Net Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D45" s="19" t="inlineStr">
@@ -2771,10 +2792,10 @@
         </is>
       </c>
       <c r="E45" s="10" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -2790,17 +2811,17 @@
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>GD1009318131514</t>
+          <t>GD1010137931149</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>Front End Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>iSHR</t>
+          <t>BP p.l.c.</t>
         </is>
       </c>
       <c r="D46" s="19" t="inlineStr">
@@ -2809,7 +2830,7 @@
         </is>
       </c>
       <c r="E46" s="10" t="n">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>0.9999</v>
@@ -2828,17 +2849,17 @@
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>GD1010016373072</t>
+          <t>GD1005863473199</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence (Data Analyst)</t>
+          <t>Software Development Engineer I - SDE I</t>
         </is>
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>Pinnacle Consultz</t>
         </is>
       </c>
       <c r="D47" s="19" t="inlineStr">
@@ -2847,7 +2868,7 @@
         </is>
       </c>
       <c r="E47" s="10" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>0.9999</v>
@@ -2866,17 +2887,17 @@
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>GD1009780088072</t>
+          <t>GD1007767904151</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Front End developer</t>
         </is>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>Fireblaze Technologies Pvt. Ltd</t>
+          <t>Orbiqe Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="D48" s="19" t="inlineStr">
@@ -2904,17 +2925,17 @@
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>GD1009780147845</t>
+          <t>GD1007935453441</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst (SQL)</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>Games2win India Pvt. Ltd.</t>
+          <t>E2M Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -2942,17 +2963,17 @@
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>GD1010162585916</t>
+          <t>GD1010003092577</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Frontend Developer (React+Nextjs)</t>
         </is>
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finastra </t>
+          <t>NUOX Technologies</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
@@ -2961,7 +2982,7 @@
         </is>
       </c>
       <c r="E50" s="10" t="n">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>0.9999</v>
@@ -2980,17 +3001,17 @@
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>GD1009784661520</t>
+          <t>GD1010173782303</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst / Biostatistician</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>Rehoboth Academic Services</t>
+          <t>UBS AG</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
@@ -2999,7 +3020,7 @@
         </is>
       </c>
       <c r="E51" s="10" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="F51" s="11" t="n">
         <v>0.9999</v>
@@ -3018,17 +3039,17 @@
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>GD1009650393787</t>
+          <t>GD1010166514208</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>Business Analytics Analyst</t>
+          <t>Business Data Analyst</t>
         </is>
       </c>
       <c r="C52" s="19" t="inlineStr">
         <is>
-          <t>INTIGNIZ Solutions Private Limited</t>
+          <t>JK Technosoft Limited</t>
         </is>
       </c>
       <c r="D52" s="19" t="inlineStr">
@@ -3037,7 +3058,7 @@
         </is>
       </c>
       <c r="E52" s="10" t="n">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F52" s="11" t="n">
         <v>0.9999</v>
@@ -3056,17 +3077,17 @@
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>GD1005957142708</t>
+          <t>GD1009227091208</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t>Full Stack UI Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>WPoets Technology LLP</t>
+          <t>ekZero Corporation</t>
         </is>
       </c>
       <c r="D53" s="19" t="inlineStr">
@@ -3075,7 +3096,7 @@
         </is>
       </c>
       <c r="E53" s="10" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F53" s="11" t="n">
         <v>0.9999</v>
@@ -3094,17 +3115,17 @@
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>GD1009724595329</t>
+          <t>GD1010037476315</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>Sr Frontend Engineer</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>Excel Net Solutions Pvt. Ltd.</t>
+          <t>InOpTra Digital Pvt Ltd</t>
         </is>
       </c>
       <c r="D54" s="19" t="inlineStr">
@@ -3113,7 +3134,7 @@
         </is>
       </c>
       <c r="E54" s="10" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F54" s="11" t="n">
         <v>0.9999</v>
@@ -3132,17 +3153,17 @@
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>GD1010057179983</t>
+          <t>GD1009978326750</t>
         </is>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>AI/ML Engineers</t>
+          <t>Jr. Frontend Developer Executive</t>
         </is>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions, Inc.</t>
+          <t>FashionTV India PVT LTD</t>
         </is>
       </c>
       <c r="D55" s="19" t="inlineStr">
@@ -3151,10 +3172,10 @@
         </is>
       </c>
       <c r="E55" s="10" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -3170,17 +3191,17 @@
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>GD1009433735056</t>
+          <t>GD1009650393787</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Business Analytics Analyst</t>
         </is>
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>Awapal Solutions Pvt. Ltd.</t>
+          <t>INTIGNIZ Solutions Private Limited</t>
         </is>
       </c>
       <c r="D56" s="19" t="inlineStr">
@@ -3189,10 +3210,10 @@
         </is>
       </c>
       <c r="E56" s="10" t="n">
-        <v>137</v>
+        <v>365</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -3208,17 +3229,17 @@
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>GD1006034255929</t>
+          <t>GD1009290074713</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>Front End Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>TraveloPro</t>
+          <t>Indian Internet Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D57" s="19" t="inlineStr">
@@ -3227,10 +3248,10 @@
         </is>
       </c>
       <c r="E57" s="10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -3246,17 +3267,17 @@
     <row r="58">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>GD1009902680489</t>
+          <t>GD1010016373072</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>Data Engineer (LLM Data Pipeline)</t>
+          <t>Senior Analyst - Business Intelligence (Data Analyst)</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Building Blocks Software Services</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="D58" s="19" t="inlineStr">
@@ -3265,10 +3286,10 @@
         </is>
       </c>
       <c r="E58" s="10" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -3284,17 +3305,17 @@
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>GD1007467247069</t>
+          <t>GD1007954581337</t>
         </is>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>React Js Developer</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t>Rrayze Business Solutions</t>
+          <t>Brown Button Private Limited</t>
         </is>
       </c>
       <c r="D59" s="19" t="inlineStr">
@@ -3306,7 +3327,7 @@
         <v>130</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -3322,17 +3343,17 @@
     <row r="60">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>GD1009972605237</t>
+          <t>GD1009269345936</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Senior UI/Frontend Developer</t>
         </is>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>Xiarch Solutions Private Limited</t>
+          <t xml:space="preserve">Pivox Labs </t>
         </is>
       </c>
       <c r="D60" s="19" t="inlineStr">
@@ -3341,10 +3362,10 @@
         </is>
       </c>
       <c r="E60" s="10" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -3353,24 +3374,24 @@
       </c>
       <c r="H60" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>GD1009790591797</t>
+          <t>GD1009947953274</t>
         </is>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Fresher Python AI/ML Developer</t>
         </is>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>United Parcel Service, Inc.</t>
+          <t>Shine Infosoft</t>
         </is>
       </c>
       <c r="D61" s="19" t="inlineStr">
@@ -3379,10 +3400,10 @@
         </is>
       </c>
       <c r="E61" s="10" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -3398,17 +3419,17 @@
     <row r="62">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>GD1009563892630</t>
+          <t>GD1005957142708</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>ReactJS developer</t>
+          <t>Full Stack UI Developer</t>
         </is>
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netfillip Technologies Private Limited </t>
+          <t>WPoets Technology LLP</t>
         </is>
       </c>
       <c r="D62" s="19" t="inlineStr">
@@ -3417,7 +3438,7 @@
         </is>
       </c>
       <c r="E62" s="10" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F62" s="11" t="n">
         <v>0.9998</v>
@@ -3436,17 +3457,17 @@
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>GD1010164982406</t>
+          <t>GD1009788088069</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>Lead Product Software Engineer - React.js/NodeJS/AngularJS</t>
+          <t>Jr. Automation Engineer</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>Wolters Kluwer nv</t>
+          <t>Jabil Circuit, Inc.</t>
         </is>
       </c>
       <c r="D63" s="19" t="inlineStr">
@@ -3455,7 +3476,7 @@
         </is>
       </c>
       <c r="E63" s="10" t="n">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="F63" s="11" t="n">
         <v>0.9998</v>
@@ -3512,17 +3533,17 @@
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>GD1009065281506</t>
+          <t>GD1010164982406</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>Front End Developer</t>
+          <t>Lead Product Software Engineer - React.js/NodeJS/AngularJS</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>Codeclouds IT Solutions Pvt. Ltd.</t>
+          <t>Wolters Kluwer nv</t>
         </is>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -3531,7 +3552,7 @@
         </is>
       </c>
       <c r="E65" s="10" t="n">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="F65" s="11" t="n">
         <v>0.9998</v>
@@ -3550,17 +3571,17 @@
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>GD1009686139823</t>
+          <t>GD1010087875504</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>Front End Engineer</t>
+          <t>Frontend / Webflow Developer</t>
         </is>
       </c>
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eastern Book Co. (P) Ltd. </t>
+          <t>MetaDesign Solutions</t>
         </is>
       </c>
       <c r="D66" s="19" t="inlineStr">
@@ -3569,7 +3590,7 @@
         </is>
       </c>
       <c r="E66" s="10" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="F66" s="11" t="n">
         <v>0.9998</v>
@@ -3588,17 +3609,17 @@
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>GD1009424315122</t>
+          <t>GD1010170139132</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Engineer II - Software</t>
         </is>
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>Equiniti</t>
+          <t>Microchip Technology Incorporated</t>
         </is>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -3607,7 +3628,7 @@
         </is>
       </c>
       <c r="E67" s="10" t="n">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="F67" s="11" t="n">
         <v>0.9998</v>
@@ -3626,17 +3647,17 @@
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>GD1010060640618</t>
+          <t>GD1010141561000</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Inventory Analyst</t>
         </is>
       </c>
       <c r="C68" s="19" t="inlineStr">
         <is>
-          <t>Codeclouds IT Solutions Pvt. Ltd.</t>
+          <t>Jabil Circuit, Inc.</t>
         </is>
       </c>
       <c r="D68" s="19" t="inlineStr">
@@ -3645,10 +3666,10 @@
         </is>
       </c>
       <c r="E68" s="10" t="n">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9997</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -3664,29 +3685,29 @@
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>GD1010183680098</t>
+          <t>LI4306122383</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>Junior Developer</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>Mouser Electronics, Inc.</t>
+          <t>Instazen Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E69" s="10" t="n">
-        <v>6</v>
+        <v>280</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9997</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -3695,24 +3716,24 @@
       </c>
       <c r="H69" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>GD1010006271334</t>
+          <t>GD1010166833932</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer</t>
+          <t>Lead Service Analyst - Data Services</t>
         </is>
       </c>
       <c r="C70" s="19" t="inlineStr">
         <is>
-          <t>Barclays PLC</t>
+          <t>Société Générale</t>
         </is>
       </c>
       <c r="D70" s="19" t="inlineStr">
@@ -3721,10 +3742,10 @@
         </is>
       </c>
       <c r="E70" s="10" t="n">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9997</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
@@ -3740,17 +3761,17 @@
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
         <is>
-          <t>GD1010171680953</t>
+          <t>GD1010133055445</t>
         </is>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>SAS Data analyst</t>
+          <t>Business Insights &amp; Development Analyst</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>Citigroup Inc.</t>
+          <t xml:space="preserve">Hong Kong Aircraft Engineering Company Limited </t>
         </is>
       </c>
       <c r="D71" s="19" t="inlineStr">
@@ -3759,10 +3780,10 @@
         </is>
       </c>
       <c r="E71" s="10" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9997</v>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
@@ -3778,17 +3799,17 @@
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>GD1010029737159</t>
+          <t>GD1007856515877</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. UI / FRONTEND DEVELOPER</t>
         </is>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>Paarsh Infotech</t>
+          <t>Northcorp Software Pvt Ltd</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
@@ -3797,10 +3818,10 @@
         </is>
       </c>
       <c r="E72" s="10" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>0.9998</v>
+        <v>0.9997</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
@@ -3809,24 +3830,24 @@
       </c>
       <c r="H72" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>GD1010027266260</t>
+          <t>GD1007999449903</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Fulltime React.js / Node js Developer</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>Hilti Corporation</t>
+          <t>Litost India Infotech Pvt Ltd</t>
         </is>
       </c>
       <c r="D73" s="19" t="inlineStr">
@@ -3835,7 +3856,7 @@
         </is>
       </c>
       <c r="E73" s="10" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F73" s="11" t="n">
         <v>0.9997</v>
@@ -3854,17 +3875,17 @@
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>GD1010165886307</t>
+          <t>GD1009901589738</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>SMI Data Analyst 1</t>
+          <t>Frontend Developer (HTML)</t>
         </is>
       </c>
       <c r="C74" s="19" t="inlineStr">
         <is>
-          <t>RSM International Ltd.</t>
+          <t>Informica Solutions</t>
         </is>
       </c>
       <c r="D74" s="19" t="inlineStr">
@@ -3873,7 +3894,7 @@
         </is>
       </c>
       <c r="E74" s="10" t="n">
-        <v>25</v>
+        <v>271</v>
       </c>
       <c r="F74" s="11" t="n">
         <v>0.9997</v>
@@ -3892,17 +3913,17 @@
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>GD1010177029336</t>
+          <t>GD1010036467238</t>
         </is>
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>Digital Software Engineer Senior Analyst - Web Development</t>
+          <t>Front End Developer</t>
         </is>
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
-          <t>Citigroup Inc.</t>
+          <t>Transcorp International Ltd</t>
         </is>
       </c>
       <c r="D75" s="19" t="inlineStr">
@@ -3911,7 +3932,7 @@
         </is>
       </c>
       <c r="E75" s="10" t="n">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="F75" s="11" t="n">
         <v>0.9997</v>
@@ -3923,24 +3944,24 @@
       </c>
       <c r="H75" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>GD1010168827918</t>
+          <t>GD1010156826705</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>GSCC Senior Manager</t>
+          <t>Staff Software Engineer, Frontend</t>
         </is>
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>Pinkerton</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="D76" s="19" t="inlineStr">
@@ -3949,7 +3970,7 @@
         </is>
       </c>
       <c r="E76" s="10" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F76" s="11" t="n">
         <v>0.9997</v>
@@ -3968,17 +3989,17 @@
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
         <is>
-          <t>GD1008011539630</t>
+          <t>GD1008546131448</t>
         </is>
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ReactJS Developer</t>
         </is>
       </c>
       <c r="C77" s="19" t="inlineStr">
         <is>
-          <t>Ideapoke Technologies Pvt. Ltd</t>
+          <t>Appsly Infotech</t>
         </is>
       </c>
       <c r="D77" s="19" t="inlineStr">
@@ -3987,10 +4008,10 @@
         </is>
       </c>
       <c r="E77" s="10" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>0.9997</v>
+        <v>0.9996</v>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
@@ -4006,17 +4027,17 @@
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>GD1009947953274</t>
+          <t>GD1009966575923</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>Fresher Python AI/ML Developer</t>
+          <t>LLM / Generative AI Engineer</t>
         </is>
       </c>
       <c r="C78" s="19" t="inlineStr">
         <is>
-          <t>Shine Infosoft</t>
+          <t>Refrens Internet Pvt. Ltd</t>
         </is>
       </c>
       <c r="D78" s="19" t="inlineStr">
@@ -4025,10 +4046,10 @@
         </is>
       </c>
       <c r="E78" s="10" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>0.9997</v>
+        <v>0.9996</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
@@ -4044,29 +4065,29 @@
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>GD1010068823925</t>
+          <t>LI4306114556</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Software Engineer Python</t>
         </is>
       </c>
       <c r="C79" s="19" t="inlineStr">
         <is>
-          <t>Everestek LLC</t>
+          <t>Pinnacle Seven Technologies</t>
         </is>
       </c>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E79" s="10" t="n">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>0.9997</v>
+        <v>0.9996</v>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
@@ -4075,24 +4096,24 @@
       </c>
       <c r="H79" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="19" t="inlineStr">
         <is>
-          <t>GD1009957476095</t>
+          <t>GD1006877162145</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (Chennai/Coimbatore)</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="C80" s="19" t="inlineStr">
         <is>
-          <t>Informica Solutions</t>
+          <t>Click Informatics</t>
         </is>
       </c>
       <c r="D80" s="19" t="inlineStr">
@@ -4101,10 +4122,10 @@
         </is>
       </c>
       <c r="E80" s="10" t="n">
-        <v>216</v>
+        <v>130</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>0.9997</v>
+        <v>0.9996</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
@@ -4120,17 +4141,17 @@
     <row r="81">
       <c r="A81" s="19" t="inlineStr">
         <is>
-          <t>GD1009650130305</t>
+          <t>GD1010150210469</t>
         </is>
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>Front end Designer and Developer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="C81" s="19" t="inlineStr">
         <is>
-          <t>Creative Web Designers (I) Pvt. Ltd.</t>
+          <t>Blackbuck Insights, LLC</t>
         </is>
       </c>
       <c r="D81" s="19" t="inlineStr">
@@ -4139,7 +4160,7 @@
         </is>
       </c>
       <c r="E81" s="10" t="n">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="F81" s="11" t="n">
         <v>0.9996</v>
@@ -4151,24 +4172,24 @@
       </c>
       <c r="H81" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>GD1009269345936</t>
+          <t>GD1009211007543</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>Senior UI/Frontend Developer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="C82" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pivox Labs </t>
+          <t xml:space="preserve">Wonder Home Finance Ltd </t>
         </is>
       </c>
       <c r="D82" s="19" t="inlineStr">
@@ -4177,7 +4198,7 @@
         </is>
       </c>
       <c r="E82" s="10" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F82" s="11" t="n">
         <v>0.9996</v>
@@ -4196,26 +4217,26 @@
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>GD1010003092577</t>
+          <t>LI4306118473</t>
         </is>
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer (React+Nextjs)</t>
+          <t>Frontend-React.js</t>
         </is>
       </c>
       <c r="C83" s="19" t="inlineStr">
         <is>
-          <t>NUOX Technologies</t>
+          <t>Primathon</t>
         </is>
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E83" s="10" t="n">
-        <v>132</v>
+        <v>280</v>
       </c>
       <c r="F83" s="11" t="n">
         <v>0.9996</v>
@@ -4227,24 +4248,24 @@
       </c>
       <c r="H83" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>GD1009704436666</t>
+          <t>GD1010173423734</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
         <is>
-          <t>Software Engineer -JAVA</t>
+          <t>Master Data Analyst - Cellasto</t>
         </is>
       </c>
       <c r="C84" s="19" t="inlineStr">
         <is>
-          <t>Kizora Software Private Limited</t>
+          <t>BASF Group</t>
         </is>
       </c>
       <c r="D84" s="19" t="inlineStr">
@@ -4253,7 +4274,7 @@
         </is>
       </c>
       <c r="E84" s="10" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="F84" s="11" t="n">
         <v>0.9996</v>
@@ -4272,17 +4293,17 @@
     <row r="85">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>GD1010166833932</t>
+          <t>GD1009780147845</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>Lead Service Analyst - Data Services</t>
+          <t>Data Analyst (SQL)</t>
         </is>
       </c>
       <c r="C85" s="19" t="inlineStr">
         <is>
-          <t>Société Générale</t>
+          <t>Games2win India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D85" s="19" t="inlineStr">
@@ -4291,10 +4312,10 @@
         </is>
       </c>
       <c r="E85" s="10" t="n">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0.9996</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
@@ -4310,17 +4331,17 @@
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
         <is>
-          <t>GD1010067307304</t>
+          <t>GD1010173324197</t>
         </is>
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>Jr. Frontend Developer</t>
+          <t>Workday Reporting Analyst</t>
         </is>
       </c>
       <c r="C86" s="19" t="inlineStr">
         <is>
-          <t>Enzigma Software Pvt. Ltd.</t>
+          <t>Technology Next</t>
         </is>
       </c>
       <c r="D86" s="19" t="inlineStr">
@@ -4329,10 +4350,10 @@
         </is>
       </c>
       <c r="E86" s="10" t="n">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>0.9996</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
@@ -4348,17 +4369,17 @@
     <row r="87">
       <c r="A87" s="19" t="inlineStr">
         <is>
-          <t>GD1008904426852</t>
+          <t>GD1010165113571</t>
         </is>
       </c>
       <c r="B87" s="19" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Product &amp; AI Transformation Lead (Talent Development)</t>
         </is>
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t>Rishi FIBC Solutions Pvt. Ltd</t>
+          <t>PropertyGuru Group</t>
         </is>
       </c>
       <c r="D87" s="19" t="inlineStr">
@@ -4367,10 +4388,10 @@
         </is>
       </c>
       <c r="E87" s="10" t="n">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>0.9996</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
@@ -4386,17 +4407,17 @@
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>GD1010141561000</t>
+          <t>GD1009957476095</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>Inventory Analyst</t>
+          <t>Senior Machine Learning Engineer - Hybrid (Chennai/Coimbatore)</t>
         </is>
       </c>
       <c r="C88" s="19" t="inlineStr">
         <is>
-          <t>Jabil Circuit, Inc.</t>
+          <t>Informica Solutions</t>
         </is>
       </c>
       <c r="D88" s="19" t="inlineStr">
@@ -4405,7 +4426,7 @@
         </is>
       </c>
       <c r="E88" s="10" t="n">
-        <v>46</v>
+        <v>216</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>0.9995000000000001</v>
@@ -4424,17 +4445,17 @@
     <row r="89">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>GD1009286502053</t>
+          <t>GD1005649563038</t>
         </is>
       </c>
       <c r="B89" s="19" t="inlineStr">
         <is>
-          <t>Trainee - Frontend</t>
+          <t>WEB DEVELOPER</t>
         </is>
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>Safetrax</t>
+          <t>B2L Mobitech pvt Ltd</t>
         </is>
       </c>
       <c r="D89" s="19" t="inlineStr">
@@ -4443,7 +4464,7 @@
         </is>
       </c>
       <c r="E89" s="10" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F89" s="11" t="n">
         <v>0.9995000000000001</v>
@@ -4462,17 +4483,17 @@
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
         <is>
-          <t>GD1006649775121</t>
+          <t>GD1006041114241</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer (Angular, JavaScript, Lighthouse Performance Testing)</t>
+          <t>Frontend Developer-ReactJS/AngularJS</t>
         </is>
       </c>
       <c r="C90" s="19" t="inlineStr">
         <is>
-          <t>Mobile Programming LLC</t>
+          <t>Nuchange Informatics</t>
         </is>
       </c>
       <c r="D90" s="19" t="inlineStr">
@@ -4500,17 +4521,17 @@
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>GD1010154687661</t>
+          <t>GD1010137384215</t>
         </is>
       </c>
       <c r="B91" s="19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Weather Data Scientist (Data Assimilation)</t>
         </is>
       </c>
       <c r="C91" s="19" t="inlineStr">
         <is>
-          <t>ATS Corporation</t>
+          <t>Pravah</t>
         </is>
       </c>
       <c r="D91" s="19" t="inlineStr">
@@ -4519,7 +4540,7 @@
         </is>
       </c>
       <c r="E91" s="10" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F91" s="11" t="n">
         <v>0.9995000000000001</v>
@@ -4538,17 +4559,17 @@
     <row r="92">
       <c r="A92" s="19" t="inlineStr">
         <is>
-          <t>GD1010170139132</t>
+          <t>GD1010137384217</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>Engineer II - Software</t>
+          <t>Weather Data Scientist (Numerical Weather Prediction)</t>
         </is>
       </c>
       <c r="C92" s="19" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>Pravah</t>
         </is>
       </c>
       <c r="D92" s="19" t="inlineStr">
@@ -4557,7 +4578,7 @@
         </is>
       </c>
       <c r="E92" s="10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F92" s="11" t="n">
         <v>0.9995000000000001</v>
@@ -4576,17 +4597,17 @@
     <row r="93">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>GD1010120053957</t>
+          <t>GD1009318131514</t>
         </is>
       </c>
       <c r="B93" s="19" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Front End Developer</t>
         </is>
       </c>
       <c r="C93" s="19" t="inlineStr">
         <is>
-          <t>Antino Labs</t>
+          <t>iSHR</t>
         </is>
       </c>
       <c r="D93" s="19" t="inlineStr">
@@ -4595,10 +4616,10 @@
         </is>
       </c>
       <c r="E93" s="10" t="n">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
@@ -4614,17 +4635,17 @@
     <row r="94">
       <c r="A94" s="19" t="inlineStr">
         <is>
-          <t>GD1010186703724</t>
+          <t>GD1010166417609</t>
         </is>
       </c>
       <c r="B94" s="19" t="inlineStr">
         <is>
-          <t>Sr. Software Platform Engineer II</t>
+          <t>Front-end React Engineer</t>
         </is>
       </c>
       <c r="C94" s="19" t="inlineStr">
         <is>
-          <t>MetLife, Inc.</t>
+          <t>Quest Global Services Pte. Ltd.</t>
         </is>
       </c>
       <c r="D94" s="19" t="inlineStr">
@@ -4633,10 +4654,10 @@
         </is>
       </c>
       <c r="E94" s="10" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
@@ -4645,24 +4666,24 @@
       </c>
       <c r="H94" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>GD1010166514208</t>
+          <t>GD1010186159038</t>
         </is>
       </c>
       <c r="B95" s="19" t="inlineStr">
         <is>
-          <t>Business Data Analyst</t>
+          <t>Sr. Gen AI Engineer</t>
         </is>
       </c>
       <c r="C95" s="19" t="inlineStr">
         <is>
-          <t>JK Technosoft Limited</t>
+          <t>GAVS Technologies Private Limited</t>
         </is>
       </c>
       <c r="D95" s="19" t="inlineStr">
@@ -4671,10 +4692,10 @@
         </is>
       </c>
       <c r="E95" s="10" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
@@ -4683,24 +4704,24 @@
       </c>
       <c r="H95" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="19" t="inlineStr">
         <is>
-          <t>GD1010188213677</t>
+          <t>GD1009286502053</t>
         </is>
       </c>
       <c r="B96" s="19" t="inlineStr">
         <is>
-          <t>Software/Platform Engineer I</t>
+          <t>Trainee - Frontend</t>
         </is>
       </c>
       <c r="C96" s="19" t="inlineStr">
         <is>
-          <t>MetLife, Inc.</t>
+          <t>Safetrax</t>
         </is>
       </c>
       <c r="D96" s="19" t="inlineStr">
@@ -4709,10 +4730,10 @@
         </is>
       </c>
       <c r="E96" s="10" t="n">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
@@ -4721,24 +4742,24 @@
       </c>
       <c r="H96" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="19" t="inlineStr">
         <is>
-          <t>GD1009853609992</t>
+          <t>GD1008904426852</t>
         </is>
       </c>
       <c r="B97" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Analysis</t>
         </is>
       </c>
       <c r="C97" s="19" t="inlineStr">
         <is>
-          <t>Dantech Engenharia</t>
+          <t>Rishi FIBC Solutions Pvt. Ltd</t>
         </is>
       </c>
       <c r="D97" s="19" t="inlineStr">
@@ -4747,10 +4768,10 @@
         </is>
       </c>
       <c r="E97" s="10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
@@ -4766,17 +4787,17 @@
     <row r="98">
       <c r="A98" s="19" t="inlineStr">
         <is>
-          <t>GD1009625774601</t>
+          <t>GD1009780088072</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>Junior Consultant – Data Analyst(Contract)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C98" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recruber </t>
+          <t>Fireblaze Technologies Pvt. Ltd</t>
         </is>
       </c>
       <c r="D98" s="19" t="inlineStr">
@@ -4785,10 +4806,10 @@
         </is>
       </c>
       <c r="E98" s="10" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
@@ -4797,24 +4818,24 @@
       </c>
       <c r="H98" s="19" t="inlineStr">
         <is>
-          <t>days_live</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="19" t="inlineStr">
         <is>
-          <t>GD1008270450249</t>
+          <t>GD1010162585916</t>
         </is>
       </c>
       <c r="B99" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C99" s="19" t="inlineStr">
         <is>
-          <t>Careervira</t>
+          <t xml:space="preserve">Finastra </t>
         </is>
       </c>
       <c r="D99" s="19" t="inlineStr">
@@ -4823,10 +4844,10 @@
         </is>
       </c>
       <c r="E99" s="10" t="n">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
@@ -4835,24 +4856,24 @@
       </c>
       <c r="H99" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="19" t="inlineStr">
         <is>
-          <t>GD1010171807084</t>
+          <t>GD1010170069400</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
         <is>
-          <t>Data and Analytics Managing Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="C100" s="19" t="inlineStr">
         <is>
-          <t>NTT DATA GROUP Corporation</t>
+          <t xml:space="preserve">Finastra </t>
         </is>
       </c>
       <c r="D100" s="19" t="inlineStr">
@@ -4861,10 +4882,10 @@
         </is>
       </c>
       <c r="E100" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
@@ -4880,17 +4901,17 @@
     <row r="101">
       <c r="A101" s="19" t="inlineStr">
         <is>
-          <t>GD1009901589738</t>
+          <t>GD1009960227232</t>
         </is>
       </c>
       <c r="B101" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer (HTML)</t>
+          <t>React JS Developer</t>
         </is>
       </c>
       <c r="C101" s="19" t="inlineStr">
         <is>
-          <t>Informica Solutions</t>
+          <t>HorizonCore InfoSoft Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D101" s="19" t="inlineStr">
@@ -4899,10 +4920,10 @@
         </is>
       </c>
       <c r="E101" s="10" t="n">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
@@ -4911,24 +4932,24 @@
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="19" t="inlineStr">
         <is>
-          <t>GD1007754610218</t>
+          <t>GD1009972605237</t>
         </is>
       </c>
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>JavaScript Frontend Developer</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="C102" s="19" t="inlineStr">
         <is>
-          <t>DesignnBuy Pvt Ltd</t>
+          <t>Xiarch Solutions Private Limited</t>
         </is>
       </c>
       <c r="D102" s="19" t="inlineStr">
@@ -4940,7 +4961,7 @@
         <v>137</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
@@ -4956,17 +4977,17 @@
     <row r="103">
       <c r="A103" s="19" t="inlineStr">
         <is>
-          <t>GD1010169982642</t>
+          <t>GD1009767220977</t>
         </is>
       </c>
       <c r="B103" s="19" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer (Frontend)</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="C103" s="19" t="inlineStr">
         <is>
-          <t>Mott MacDonald Group Limited</t>
+          <t>Spacedge Creation</t>
         </is>
       </c>
       <c r="D103" s="19" t="inlineStr">
@@ -4975,10 +4996,10 @@
         </is>
       </c>
       <c r="E103" s="10" t="n">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
@@ -4994,29 +5015,29 @@
     <row r="104">
       <c r="A104" s="19" t="inlineStr">
         <is>
-          <t>GD1009606712806</t>
+          <t>LI4306114548</t>
         </is>
       </c>
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="C104" s="19" t="inlineStr">
         <is>
-          <t>LogicHive Solutions Pvt Ltd</t>
+          <t>WEQ Technologies</t>
         </is>
       </c>
       <c r="D104" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E104" s="10" t="n">
-        <v>365</v>
+        <v>280</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
@@ -5025,24 +5046,24 @@
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="19" t="inlineStr">
         <is>
-          <t>GD1008233108435</t>
+          <t>GD1010088776550</t>
         </is>
       </c>
       <c r="B105" s="19" t="inlineStr">
         <is>
-          <t>Back-end Developer</t>
+          <t>IFC Data - Business Analyst</t>
         </is>
       </c>
       <c r="C105" s="19" t="inlineStr">
         <is>
-          <t>Riaxe Systems</t>
+          <t>Barclays PLC</t>
         </is>
       </c>
       <c r="D105" s="19" t="inlineStr">
@@ -5051,10 +5072,10 @@
         </is>
       </c>
       <c r="E105" s="10" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993</v>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
@@ -5070,17 +5091,17 @@
     <row r="106">
       <c r="A106" s="19" t="inlineStr">
         <is>
-          <t>GD1009422806620</t>
+          <t>GD1010178130737</t>
         </is>
       </c>
       <c r="B106" s="19" t="inlineStr">
         <is>
-          <t>Sr. Power Bi Developer</t>
+          <t>Business Analyst - Associate</t>
         </is>
       </c>
       <c r="C106" s="19" t="inlineStr">
         <is>
-          <t>TechTree IT Systems Pvt Ltd.</t>
+          <t>KG Information Systems Private Limited</t>
         </is>
       </c>
       <c r="D106" s="19" t="inlineStr">
@@ -5089,10 +5110,10 @@
         </is>
       </c>
       <c r="E106" s="10" t="n">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>0.9994</v>
+        <v>0.9992</v>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
@@ -5101,24 +5122,24 @@
       </c>
       <c r="H106" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="19" t="inlineStr">
         <is>
-          <t>GD1009290074713</t>
+          <t>GD1010165886307</t>
         </is>
       </c>
       <c r="B107" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>SMI Data Analyst 1</t>
         </is>
       </c>
       <c r="C107" s="19" t="inlineStr">
         <is>
-          <t>Indian Internet Solutions Pvt. Ltd.</t>
+          <t>RSM International Ltd.</t>
         </is>
       </c>
       <c r="D107" s="19" t="inlineStr">
@@ -5127,10 +5148,10 @@
         </is>
       </c>
       <c r="E107" s="10" t="n">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>0.9994</v>
+        <v>0.9992</v>
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
@@ -5139,24 +5160,24 @@
       </c>
       <c r="H107" s="19" t="inlineStr">
         <is>
-          <t>days_live</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="19" t="inlineStr">
         <is>
-          <t>GD1010160942923</t>
+          <t>GD1006367490721</t>
         </is>
       </c>
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>Quality Data Analytics Engineer</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="C108" s="19" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Govche India Private Limited</t>
         </is>
       </c>
       <c r="D108" s="19" t="inlineStr">
@@ -5165,10 +5186,10 @@
         </is>
       </c>
       <c r="E108" s="10" t="n">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>0.9994</v>
+        <v>0.9992</v>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
@@ -5184,17 +5205,17 @@
     <row r="109">
       <c r="A109" s="19" t="inlineStr">
         <is>
-          <t>GD1010161102591</t>
+          <t>GD1009938023608</t>
         </is>
       </c>
       <c r="B109" s="19" t="inlineStr">
         <is>
-          <t>Senior PHP Developer</t>
+          <t>AI-Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C109" s="19" t="inlineStr">
         <is>
-          <t>SysCorp Technology Private Limited</t>
+          <t>V Support Solutions</t>
         </is>
       </c>
       <c r="D109" s="19" t="inlineStr">
@@ -5203,10 +5224,10 @@
         </is>
       </c>
       <c r="E109" s="10" t="n">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0.9994</v>
+        <v>0.9992</v>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
@@ -5222,17 +5243,17 @@
     <row r="110">
       <c r="A110" s="19" t="inlineStr">
         <is>
-          <t>GD1010160908910</t>
+          <t>GD1009625774601</t>
         </is>
       </c>
       <c r="B110" s="19" t="inlineStr">
         <is>
-          <t>Data Scientist, Financial Analytics</t>
+          <t>Junior Consultant – Data Analyst(Contract)</t>
         </is>
       </c>
       <c r="C110" s="19" t="inlineStr">
         <is>
-          <t>People Center, Inc.</t>
+          <t xml:space="preserve">Recruber </t>
         </is>
       </c>
       <c r="D110" s="19" t="inlineStr">
@@ -5241,10 +5262,10 @@
         </is>
       </c>
       <c r="E110" s="10" t="n">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>0.9994</v>
+        <v>0.9992</v>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
@@ -5260,17 +5281,17 @@
     <row r="111">
       <c r="A111" s="19" t="inlineStr">
         <is>
-          <t>GD1006877162145</t>
+          <t>GD1007873531275</t>
         </is>
       </c>
       <c r="B111" s="19" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>UI Developer</t>
         </is>
       </c>
       <c r="C111" s="19" t="inlineStr">
         <is>
-          <t>Click Informatics</t>
+          <t>SSP Technology</t>
         </is>
       </c>
       <c r="D111" s="19" t="inlineStr">
@@ -5282,7 +5303,7 @@
         <v>130</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>0.9993</v>
+        <v>0.9991</v>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
@@ -5298,17 +5319,17 @@
     <row r="112">
       <c r="A112" s="19" t="inlineStr">
         <is>
-          <t>GD1010180341623</t>
+          <t>GD1010160908910</t>
         </is>
       </c>
       <c r="B112" s="19" t="inlineStr">
         <is>
-          <t>Front-end Engineer - GPP/P2G</t>
+          <t>Data Scientist, Financial Analytics</t>
         </is>
       </c>
       <c r="C112" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finastra </t>
+          <t>People Center, Inc.</t>
         </is>
       </c>
       <c r="D112" s="19" t="inlineStr">
@@ -5317,10 +5338,10 @@
         </is>
       </c>
       <c r="E112" s="10" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>0.9993</v>
+        <v>0.9991</v>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
@@ -5329,24 +5350,24 @@
       </c>
       <c r="H112" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="19" t="inlineStr">
         <is>
-          <t>GD1008546131448</t>
+          <t>GD1007838294703</t>
         </is>
       </c>
       <c r="B113" s="19" t="inlineStr">
         <is>
-          <t>ReactJS Developer</t>
+          <t>Data Analyst (ETL Tools)</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>Appsly Infotech</t>
+          <t>Alpha Analytics Services Private Limited</t>
         </is>
       </c>
       <c r="D113" s="19" t="inlineStr">
@@ -5355,10 +5376,10 @@
         </is>
       </c>
       <c r="E113" s="10" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>0.9993</v>
+        <v>0.9991</v>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
@@ -5374,17 +5395,17 @@
     <row r="114">
       <c r="A114" s="19" t="inlineStr">
         <is>
-          <t>GD1010133055445</t>
+          <t>GD1009396668754</t>
         </is>
       </c>
       <c r="B114" s="19" t="inlineStr">
         <is>
-          <t>Business Insights &amp; Development Analyst</t>
+          <t>Front End Developer</t>
         </is>
       </c>
       <c r="C114" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hong Kong Aircraft Engineering Company Limited </t>
+          <t xml:space="preserve">JAWK Softwares </t>
         </is>
       </c>
       <c r="D114" s="19" t="inlineStr">
@@ -5393,10 +5414,10 @@
         </is>
       </c>
       <c r="E114" s="10" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>0.9993</v>
+        <v>0.9991</v>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
@@ -5412,17 +5433,17 @@
     <row r="115">
       <c r="A115" s="19" t="inlineStr">
         <is>
-          <t>GD1010188320452</t>
+          <t>GD1009902680489</t>
         </is>
       </c>
       <c r="B115" s="19" t="inlineStr">
         <is>
-          <t>Sr. Frontend Developer (CMS Prismic)</t>
+          <t>Data Engineer (LLM Data Pipeline)</t>
         </is>
       </c>
       <c r="C115" s="19" t="inlineStr">
         <is>
-          <t>Genpact Limited</t>
+          <t xml:space="preserve"> Building Blocks Software Services</t>
         </is>
       </c>
       <c r="D115" s="19" t="inlineStr">
@@ -5431,10 +5452,10 @@
         </is>
       </c>
       <c r="E115" s="10" t="n">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>0.9992</v>
+        <v>0.9991</v>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
@@ -5443,24 +5464,24 @@
       </c>
       <c r="H115" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="19" t="inlineStr">
         <is>
-          <t>GD1009978327120</t>
+          <t>GD1010168827918</t>
         </is>
       </c>
       <c r="B116" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer Manager</t>
+          <t>GSCC Senior Manager</t>
         </is>
       </c>
       <c r="C116" s="19" t="inlineStr">
         <is>
-          <t>FashionTV India PVT LTD</t>
+          <t>Pinkerton</t>
         </is>
       </c>
       <c r="D116" s="19" t="inlineStr">
@@ -5469,10 +5490,10 @@
         </is>
       </c>
       <c r="E116" s="10" t="n">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>0.9992</v>
+        <v>0.999</v>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
@@ -5481,24 +5502,24 @@
       </c>
       <c r="H116" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="19" t="inlineStr">
         <is>
-          <t>GD1009396668754</t>
+          <t>GD1008297385561</t>
         </is>
       </c>
       <c r="B117" s="19" t="inlineStr">
         <is>
-          <t>Front End Developer</t>
+          <t>Jr./ Sr. Machine Learning Developer</t>
         </is>
       </c>
       <c r="C117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAWK Softwares </t>
+          <t>Vertscend Automation Pvt Ltd</t>
         </is>
       </c>
       <c r="D117" s="19" t="inlineStr">
@@ -5507,10 +5528,10 @@
         </is>
       </c>
       <c r="E117" s="10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>0.9992</v>
+        <v>0.999</v>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
@@ -5519,24 +5540,24 @@
       </c>
       <c r="H117" s="19" t="inlineStr">
         <is>
-          <t>days_live</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="19" t="inlineStr">
         <is>
-          <t>GD1010104531228</t>
+          <t>GD1010120053957</t>
         </is>
       </c>
       <c r="B118" s="19" t="inlineStr">
         <is>
-          <t>CLOUD MACHINE LEARNING ENGINEER</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="C118" s="19" t="inlineStr">
         <is>
-          <t>VodafoneThree Ltd</t>
+          <t>Antino Labs</t>
         </is>
       </c>
       <c r="D118" s="19" t="inlineStr">
@@ -5545,10 +5566,10 @@
         </is>
       </c>
       <c r="E118" s="10" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>0.9992</v>
+        <v>0.999</v>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
@@ -5564,17 +5585,17 @@
     <row r="119">
       <c r="A119" s="19" t="inlineStr">
         <is>
-          <t>GD1010036467238</t>
+          <t>GD1010169982642</t>
         </is>
       </c>
       <c r="B119" s="19" t="inlineStr">
         <is>
-          <t>Front End Developer</t>
+          <t>Senior Digital Engineer (Frontend)</t>
         </is>
       </c>
       <c r="C119" s="19" t="inlineStr">
         <is>
-          <t>Transcorp International Ltd</t>
+          <t>Mott MacDonald Group Limited</t>
         </is>
       </c>
       <c r="D119" s="19" t="inlineStr">
@@ -5583,10 +5604,10 @@
         </is>
       </c>
       <c r="E119" s="10" t="n">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>0.9992</v>
+        <v>0.999</v>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
@@ -5602,17 +5623,17 @@
     <row r="120">
       <c r="A120" s="19" t="inlineStr">
         <is>
-          <t>GD1009978326750</t>
+          <t>GD1010183654341</t>
         </is>
       </c>
       <c r="B120" s="19" t="inlineStr">
         <is>
-          <t>Jr. Frontend Developer Executive</t>
+          <t>React Js Developer</t>
         </is>
       </c>
       <c r="C120" s="19" t="inlineStr">
         <is>
-          <t>FashionTV India PVT LTD</t>
+          <t>Encoders</t>
         </is>
       </c>
       <c r="D120" s="19" t="inlineStr">
@@ -5621,10 +5642,10 @@
         </is>
       </c>
       <c r="E120" s="10" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>0.9992</v>
+        <v>0.999</v>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
@@ -5633,24 +5654,24 @@
       </c>
       <c r="H120" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="19" t="inlineStr">
         <is>
-          <t>GD1010160811554</t>
+          <t>GD1008161892624</t>
         </is>
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>Reporting Analysis - Data Analyst</t>
+          <t>UI Developer</t>
         </is>
       </c>
       <c r="C121" s="19" t="inlineStr">
         <is>
-          <t>Citigroup Inc.</t>
+          <t>SRV Info Tech</t>
         </is>
       </c>
       <c r="D121" s="19" t="inlineStr">
@@ -5659,10 +5680,10 @@
         </is>
       </c>
       <c r="E121" s="10" t="n">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
@@ -5678,17 +5699,17 @@
     <row r="122">
       <c r="A122" s="19" t="inlineStr">
         <is>
-          <t>GD1010191122465</t>
+          <t>GD1010169586676</t>
         </is>
       </c>
       <c r="B122" s="19" t="inlineStr">
         <is>
-          <t>Construction Analyst [Candidates from Navi Mumbai &amp; Thane to Kalyan]</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C122" s="19" t="inlineStr">
         <is>
-          <t>Biltrax Construction Data Research Insight &amp; Technologies Private Limited</t>
+          <t>Cognite</t>
         </is>
       </c>
       <c r="D122" s="19" t="inlineStr">
@@ -5697,10 +5718,10 @@
         </is>
       </c>
       <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
@@ -5709,24 +5730,24 @@
       </c>
       <c r="H122" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="19" t="inlineStr">
         <is>
-          <t>GD1010182525386</t>
+          <t>GD1010029737159</t>
         </is>
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
-          <t>Technical Business Analyst - Intellimatch / Smartstream</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C123" s="19" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Paarsh Infotech</t>
         </is>
       </c>
       <c r="D123" s="19" t="inlineStr">
@@ -5735,10 +5756,10 @@
         </is>
       </c>
       <c r="E123" s="10" t="n">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>0.9991</v>
+        <v>0.9989</v>
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
@@ -5747,24 +5768,24 @@
       </c>
       <c r="H123" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="19" t="inlineStr">
         <is>
-          <t>GD1008161892624</t>
+          <t>GD1009650130305</t>
         </is>
       </c>
       <c r="B124" s="19" t="inlineStr">
         <is>
-          <t>UI Developer</t>
+          <t>Front end Designer and Developer</t>
         </is>
       </c>
       <c r="C124" s="19" t="inlineStr">
         <is>
-          <t>SRV Info Tech</t>
+          <t>Creative Web Designers (I) Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D124" s="19" t="inlineStr">
@@ -5773,10 +5794,10 @@
         </is>
       </c>
       <c r="E124" s="10" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>0.9991</v>
+        <v>0.9989</v>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
@@ -5785,24 +5806,24 @@
       </c>
       <c r="H124" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>listing_age_bucket</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="19" t="inlineStr">
         <is>
-          <t>GD1010182470342</t>
+          <t>GD1007219199125</t>
         </is>
       </c>
       <c r="B125" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>UI Developer</t>
         </is>
       </c>
       <c r="C125" s="19" t="inlineStr">
         <is>
-          <t>Pratap Technocrats Private Limited</t>
+          <t>Blue Horizon Infotech</t>
         </is>
       </c>
       <c r="D125" s="19" t="inlineStr">
@@ -5811,10 +5832,10 @@
         </is>
       </c>
       <c r="E125" s="10" t="n">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>0.9991</v>
+        <v>0.9989</v>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
@@ -5823,24 +5844,24 @@
       </c>
       <c r="H125" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="19" t="inlineStr">
         <is>
-          <t>GD1010158006345</t>
+          <t>GD1010165142277</t>
         </is>
       </c>
       <c r="B126" s="19" t="inlineStr">
         <is>
-          <t>Data Operations Analyst</t>
+          <t>Data Science and AI Analyst</t>
         </is>
       </c>
       <c r="C126" s="19" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="D126" s="19" t="inlineStr">
@@ -5849,10 +5870,10 @@
         </is>
       </c>
       <c r="E126" s="10" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>0.999</v>
+        <v>0.9989</v>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
@@ -5868,17 +5889,17 @@
     <row r="127">
       <c r="A127" s="19" t="inlineStr">
         <is>
-          <t>GD1010109905399</t>
+          <t>GD1010163844877</t>
         </is>
       </c>
       <c r="B127" s="19" t="inlineStr">
         <is>
-          <t>Data Integration Analyst</t>
+          <t>Procurement Data &amp; Analytics Analyst</t>
         </is>
       </c>
       <c r="C127" s="19" t="inlineStr">
         <is>
-          <t>SAS Institute Inc.</t>
+          <t>Rolls-Royce Group plc</t>
         </is>
       </c>
       <c r="D127" s="19" t="inlineStr">
@@ -5887,10 +5908,10 @@
         </is>
       </c>
       <c r="E127" s="10" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
@@ -5906,17 +5927,17 @@
     <row r="128">
       <c r="A128" s="19" t="inlineStr">
         <is>
-          <t>GD1010183214023</t>
+          <t>GD1008952246347</t>
         </is>
       </c>
       <c r="B128" s="19" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="C128" s="19" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>RocketTEch</t>
         </is>
       </c>
       <c r="D128" s="19" t="inlineStr">
@@ -5925,10 +5946,10 @@
         </is>
       </c>
       <c r="E128" s="10" t="n">
-        <v>7</v>
+        <v>133</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
@@ -5937,24 +5958,24 @@
       </c>
       <c r="H128" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="19" t="inlineStr">
         <is>
-          <t>GD1009945322830</t>
+          <t>GD1010006271334</t>
         </is>
       </c>
       <c r="B129" s="19" t="inlineStr">
         <is>
-          <t>Manager-Data Science-Data Scientist</t>
+          <t>Full Stack Java Engineer</t>
         </is>
       </c>
       <c r="C129" s="19" t="inlineStr">
         <is>
-          <t>ExlService Holdings, Inc.</t>
+          <t>Barclays PLC</t>
         </is>
       </c>
       <c r="D129" s="19" t="inlineStr">
@@ -5963,10 +5984,10 @@
         </is>
       </c>
       <c r="E129" s="10" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
@@ -5982,17 +6003,17 @@
     <row r="130">
       <c r="A130" s="19" t="inlineStr">
         <is>
-          <t>GD1010186159038</t>
+          <t>GD1009824167887</t>
         </is>
       </c>
       <c r="B130" s="19" t="inlineStr">
         <is>
-          <t>Sr. Gen AI Engineer</t>
+          <t>Data Analytics</t>
         </is>
       </c>
       <c r="C130" s="19" t="inlineStr">
         <is>
-          <t>GAVS Technologies Private Limited</t>
+          <t>Riverstone Info Tech</t>
         </is>
       </c>
       <c r="D130" s="19" t="inlineStr">
@@ -6001,10 +6022,10 @@
         </is>
       </c>
       <c r="E130" s="10" t="n">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
@@ -6013,24 +6034,24 @@
       </c>
       <c r="H130" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="19" t="inlineStr">
         <is>
-          <t>GD1009966575923</t>
+          <t>GD1005900414928</t>
         </is>
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>LLM / Generative AI Engineer</t>
+          <t>WEB DEVELOPER (Urgent Hiring)</t>
         </is>
       </c>
       <c r="C131" s="19" t="inlineStr">
         <is>
-          <t>Refrens Internet Pvt. Ltd</t>
+          <t>WebPreneurs Pvt Ltd</t>
         </is>
       </c>
       <c r="D131" s="19" t="inlineStr">
@@ -6039,10 +6060,10 @@
         </is>
       </c>
       <c r="E131" s="10" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
@@ -6051,24 +6072,24 @@
       </c>
       <c r="H131" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="19" t="inlineStr">
         <is>
-          <t>GD1010029238562</t>
+          <t>GD1009157678232</t>
         </is>
       </c>
       <c r="B132" s="19" t="inlineStr">
         <is>
-          <t>Hiring For Machine Learning Engineer</t>
+          <t>Web Designer &amp; Developer</t>
         </is>
       </c>
       <c r="C132" s="19" t="inlineStr">
         <is>
-          <t>BSRI Solutions Pvt Ltd</t>
+          <t>InduTech IT Solutions Pvt Ltd</t>
         </is>
       </c>
       <c r="D132" s="19" t="inlineStr">
@@ -6077,10 +6098,10 @@
         </is>
       </c>
       <c r="E132" s="10" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>0.9989</v>
+        <v>0.9987</v>
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
@@ -6096,17 +6117,17 @@
     <row r="133">
       <c r="A133" s="19" t="inlineStr">
         <is>
-          <t>GD1010169586676</t>
+          <t>GD1010155316672</t>
         </is>
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior ML Engineer (NLP/GenAI)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t>Cognite</t>
+          <t>Vestas Wind Systems A/S</t>
         </is>
       </c>
       <c r="D133" s="19" t="inlineStr">
@@ -6115,10 +6136,10 @@
         </is>
       </c>
       <c r="E133" s="10" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>0.9988</v>
+        <v>0.9987</v>
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
@@ -6134,17 +6155,17 @@
     <row r="134">
       <c r="A134" s="19" t="inlineStr">
         <is>
-          <t>GD1007856515877</t>
+          <t>GD1010027266260</t>
         </is>
       </c>
       <c r="B134" s="19" t="inlineStr">
         <is>
-          <t>Sr. UI / FRONTEND DEVELOPER</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C134" s="19" t="inlineStr">
         <is>
-          <t>Northcorp Software Pvt Ltd</t>
+          <t>Hilti Corporation</t>
         </is>
       </c>
       <c r="D134" s="19" t="inlineStr">
@@ -6153,10 +6174,10 @@
         </is>
       </c>
       <c r="E134" s="10" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>0.9988</v>
+        <v>0.9987</v>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
@@ -6165,24 +6186,24 @@
       </c>
       <c r="H134" s="19" t="inlineStr">
         <is>
-          <t>days_live</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="19" t="inlineStr">
         <is>
-          <t>GD1007767904151</t>
+          <t>GD1010150220969</t>
         </is>
       </c>
       <c r="B135" s="19" t="inlineStr">
         <is>
-          <t>Front End developer</t>
+          <t>SENIOR MACHINE LEARNING ENGINEER</t>
         </is>
       </c>
       <c r="C135" s="19" t="inlineStr">
         <is>
-          <t>Orbiqe Technologies Pvt Ltd</t>
+          <t>Svitla Systems Inc.</t>
         </is>
       </c>
       <c r="D135" s="19" t="inlineStr">
@@ -6191,10 +6212,10 @@
         </is>
       </c>
       <c r="E135" s="10" t="n">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>0.9988</v>
+        <v>0.9987</v>
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
@@ -6203,24 +6224,24 @@
       </c>
       <c r="H135" s="19" t="inlineStr">
         <is>
-          <t>days_live</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="19" t="inlineStr">
         <is>
-          <t>GD1006184230755</t>
+          <t>GD1010060640618</t>
         </is>
       </c>
       <c r="B136" s="19" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C136" s="19" t="inlineStr">
         <is>
-          <t>TechiesGroup IT Solution Pvt Ltd</t>
+          <t>Codeclouds IT Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D136" s="19" t="inlineStr">
@@ -6229,10 +6250,10 @@
         </is>
       </c>
       <c r="E136" s="10" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>0.9988</v>
+        <v>0.9987</v>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
@@ -6248,17 +6269,17 @@
     <row r="137">
       <c r="A137" s="19" t="inlineStr">
         <is>
-          <t>GD1010154948927</t>
+          <t>GD1009707959183</t>
         </is>
       </c>
       <c r="B137" s="19" t="inlineStr">
         <is>
-          <t>Senior AWS Migration Engineer with Gen AI</t>
+          <t>Frontend/React JS Developer</t>
         </is>
       </c>
       <c r="C137" s="19" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>Delemont Studio</t>
         </is>
       </c>
       <c r="D137" s="19" t="inlineStr">
@@ -6267,7 +6288,7 @@
         </is>
       </c>
       <c r="E137" s="10" t="n">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="F137" s="11" t="n">
         <v>0.9987</v>
@@ -6286,17 +6307,17 @@
     <row r="138">
       <c r="A138" s="19" t="inlineStr">
         <is>
-          <t>GD1010165113571</t>
+          <t>GD1010176875477</t>
         </is>
       </c>
       <c r="B138" s="19" t="inlineStr">
         <is>
-          <t>Product &amp; AI Transformation Lead (Talent Development)</t>
+          <t>Software Engineer, AI Optimization</t>
         </is>
       </c>
       <c r="C138" s="19" t="inlineStr">
         <is>
-          <t>PropertyGuru Group</t>
+          <t>Advantest Corporation</t>
         </is>
       </c>
       <c r="D138" s="19" t="inlineStr">
@@ -6305,7 +6326,7 @@
         </is>
       </c>
       <c r="E138" s="10" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F138" s="11" t="n">
         <v>0.9987</v>
@@ -6317,24 +6338,24 @@
       </c>
       <c r="H138" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="19" t="inlineStr">
         <is>
-          <t>GD1008713225915</t>
+          <t>GD1008551659880</t>
         </is>
       </c>
       <c r="B139" s="19" t="inlineStr">
         <is>
-          <t>Web &amp; Mobile Developer</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="C139" s="19" t="inlineStr">
         <is>
-          <t>Harness Digitech Private Limited</t>
+          <t>Zimong Software Private Limited</t>
         </is>
       </c>
       <c r="D139" s="19" t="inlineStr">
@@ -6343,10 +6364,10 @@
         </is>
       </c>
       <c r="E139" s="10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>0.9987</v>
+        <v>0.9986</v>
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
@@ -6362,17 +6383,17 @@
     <row r="140">
       <c r="A140" s="19" t="inlineStr">
         <is>
-          <t>GD1007873531275</t>
+          <t>GD1010150221315</t>
         </is>
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>UI Developer</t>
+          <t>SENIOR ML ENGINEER</t>
         </is>
       </c>
       <c r="C140" s="19" t="inlineStr">
         <is>
-          <t>SSP Technology</t>
+          <t>Svitla Systems Inc.</t>
         </is>
       </c>
       <c r="D140" s="19" t="inlineStr">
@@ -6381,10 +6402,10 @@
         </is>
       </c>
       <c r="E140" s="10" t="n">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>0.9987</v>
+        <v>0.9986</v>
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
@@ -6393,24 +6414,24 @@
       </c>
       <c r="H140" s="19" t="inlineStr">
         <is>
-          <t>days_live</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="19" t="inlineStr">
         <is>
-          <t>GD1007966234404</t>
+          <t>GD1010182410096</t>
         </is>
       </c>
       <c r="B141" s="19" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Data Analyst-Application Development-Data Visualization</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
         <is>
-          <t>institute for engineers</t>
+          <t>ExlService Holdings, Inc.</t>
         </is>
       </c>
       <c r="D141" s="19" t="inlineStr">
@@ -6419,10 +6440,10 @@
         </is>
       </c>
       <c r="E141" s="10" t="n">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>0.9987</v>
+        <v>0.9986</v>
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
@@ -6431,24 +6452,24 @@
       </c>
       <c r="H141" s="19" t="inlineStr">
         <is>
-          <t>employer_repost_count</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="19" t="inlineStr">
         <is>
-          <t>GD1010180718556</t>
+          <t>GD1010096903924</t>
         </is>
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C142" s="19" t="inlineStr">
         <is>
-          <t>The Royal Bank of Scotland Group plc</t>
+          <t>Siemens AG</t>
         </is>
       </c>
       <c r="D142" s="19" t="inlineStr">
@@ -6457,10 +6478,10 @@
         </is>
       </c>
       <c r="E142" s="10" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>0.9987</v>
+        <v>0.9986</v>
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
@@ -6469,24 +6490,24 @@
       </c>
       <c r="H142" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="19" t="inlineStr">
         <is>
-          <t>GD1009767220977</t>
+          <t>GD1007989727669</t>
         </is>
       </c>
       <c r="B143" s="19" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C143" s="19" t="inlineStr">
         <is>
-          <t>Spacedge Creation</t>
+          <t>Hyperthink Systems</t>
         </is>
       </c>
       <c r="D143" s="19" t="inlineStr">
@@ -6495,10 +6516,10 @@
         </is>
       </c>
       <c r="E143" s="10" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>0.9987</v>
+        <v>0.9986</v>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
@@ -6514,29 +6535,29 @@
     <row r="144">
       <c r="A144" s="19" t="inlineStr">
         <is>
-          <t>GD1010177016034</t>
+          <t>LI4306118466</t>
         </is>
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>Workforce Analyst - Data Analytics</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="C144" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPMorganChase </t>
+          <t>Fibonalabs</t>
         </is>
       </c>
       <c r="D144" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E144" s="10" t="n">
-        <v>13</v>
+        <v>280</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>0.9987</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
@@ -6545,36 +6566,36 @@
       </c>
       <c r="H144" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="19" t="inlineStr">
         <is>
-          <t>GD1010137384217</t>
+          <t>LI4300708794</t>
         </is>
       </c>
       <c r="B145" s="19" t="inlineStr">
         <is>
-          <t>Weather Data Scientist (Numerical Weather Prediction)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C145" s="19" t="inlineStr">
         <is>
-          <t>Pravah</t>
+          <t>Encardio Rite</t>
         </is>
       </c>
       <c r="D145" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E145" s="10" t="n">
-        <v>50</v>
+        <v>295</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>0.9986</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
@@ -6583,24 +6604,24 @@
       </c>
       <c r="H145" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="19" t="inlineStr">
         <is>
-          <t>GD1009157678232</t>
+          <t>GD1010179355675</t>
         </is>
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>Web Designer &amp; Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="C146" s="19" t="inlineStr">
         <is>
-          <t>InduTech IT Solutions Pvt Ltd</t>
+          <t>Infinite Computer Solutions (India) Limited</t>
         </is>
       </c>
       <c r="D146" s="19" t="inlineStr">
@@ -6609,10 +6630,10 @@
         </is>
       </c>
       <c r="E146" s="10" t="n">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>0.9986</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
@@ -6621,24 +6642,24 @@
       </c>
       <c r="H146" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="19" t="inlineStr">
         <is>
-          <t>GD1010137384215</t>
+          <t>GD1009235618698</t>
         </is>
       </c>
       <c r="B147" s="19" t="inlineStr">
         <is>
-          <t>Weather Data Scientist (Data Assimilation)</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="C147" s="19" t="inlineStr">
         <is>
-          <t>Pravah</t>
+          <t>Softura Inc.</t>
         </is>
       </c>
       <c r="D147" s="19" t="inlineStr">
@@ -6647,10 +6668,10 @@
         </is>
       </c>
       <c r="E147" s="10" t="n">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>0.9986</v>
+        <v>0.9984</v>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
@@ -6666,17 +6687,17 @@
     <row r="148">
       <c r="A148" s="19" t="inlineStr">
         <is>
-          <t>GD1009605810137</t>
+          <t>GD1010145573372</t>
         </is>
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER</t>
+          <t>Sr Analyst, DACI Analytics</t>
         </is>
       </c>
       <c r="C148" s="19" t="inlineStr">
         <is>
-          <t>PayCraft Solutions Pvt. Ltd</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="D148" s="19" t="inlineStr">
@@ -6685,10 +6706,10 @@
         </is>
       </c>
       <c r="E148" s="10" t="n">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
@@ -6704,17 +6725,17 @@
     <row r="149">
       <c r="A149" s="19" t="inlineStr">
         <is>
-          <t>GD1010179410869</t>
+          <t>GD1010134829461</t>
         </is>
       </c>
       <c r="B149" s="19" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>SENIOR DATA ANALYST</t>
         </is>
       </c>
       <c r="C149" s="19" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>Svitla Systems Inc.</t>
         </is>
       </c>
       <c r="D149" s="19" t="inlineStr">
@@ -6723,10 +6744,10 @@
         </is>
       </c>
       <c r="E149" s="10" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
@@ -6735,36 +6756,36 @@
       </c>
       <c r="H149" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="19" t="inlineStr">
         <is>
-          <t>GD1009788088069</t>
+          <t>LI4353013794</t>
         </is>
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>Jr. Automation Engineer</t>
+          <t>Frontend Developer (ReactJS + InertiaJS)</t>
         </is>
       </c>
       <c r="C150" s="19" t="inlineStr">
         <is>
-          <t>Jabil Circuit, Inc.</t>
+          <t>Recooty</t>
         </is>
       </c>
       <c r="D150" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E150" s="10" t="n">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
@@ -6773,36 +6794,36 @@
       </c>
       <c r="H150" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="19" t="inlineStr">
         <is>
-          <t>GD1010181770843</t>
+          <t>LI4306120385</t>
         </is>
       </c>
       <c r="B151" s="19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Fullstack/Mern Developer</t>
         </is>
       </c>
       <c r="C151" s="19" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>iDreamCareer.com</t>
         </is>
       </c>
       <c r="D151" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E151" s="10" t="n">
-        <v>8</v>
+        <v>280</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
@@ -6811,24 +6832,24 @@
       </c>
       <c r="H151" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="19" t="inlineStr">
         <is>
-          <t>GD1009989921449</t>
+          <t>GD1010154687661</t>
         </is>
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C152" s="19" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>ATS Corporation</t>
         </is>
       </c>
       <c r="D152" s="19" t="inlineStr">
@@ -6837,10 +6858,10 @@
         </is>
       </c>
       <c r="E152" s="10" t="n">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
@@ -6856,17 +6877,17 @@
     <row r="153">
       <c r="A153" s="19" t="inlineStr">
         <is>
-          <t>GD1010171045995</t>
+          <t>GD1010161102591</t>
         </is>
       </c>
       <c r="B153" s="19" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Analyst</t>
+          <t>Senior PHP Developer</t>
         </is>
       </c>
       <c r="C153" s="19" t="inlineStr">
         <is>
-          <t>Optum, Inc.</t>
+          <t>SysCorp Technology Private Limited</t>
         </is>
       </c>
       <c r="D153" s="19" t="inlineStr">
@@ -6875,10 +6896,10 @@
         </is>
       </c>
       <c r="E153" s="10" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
@@ -6894,17 +6915,17 @@
     <row r="154">
       <c r="A154" s="19" t="inlineStr">
         <is>
-          <t>GD1009991584703</t>
+          <t>GD1010173424874</t>
         </is>
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Global Banking &amp; Markets-FCO Analytics-Analyst- Bengaluru</t>
         </is>
       </c>
       <c r="C154" s="19" t="inlineStr">
         <is>
-          <t>BestPeers Infosystem Pvt. Ltd.</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
       <c r="D154" s="19" t="inlineStr">
@@ -6913,10 +6934,10 @@
         </is>
       </c>
       <c r="E154" s="10" t="n">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
@@ -6932,17 +6953,17 @@
     <row r="155">
       <c r="A155" s="19" t="inlineStr">
         <is>
-          <t>GD1009707959183</t>
+          <t>GD1010057039510</t>
         </is>
       </c>
       <c r="B155" s="19" t="inlineStr">
         <is>
-          <t>Frontend/React JS Developer</t>
+          <t>Engineer, Staff - IEIOT AI Systems</t>
         </is>
       </c>
       <c r="C155" s="19" t="inlineStr">
         <is>
-          <t>Delemont Studio</t>
+          <t>Qualcomm Incorporated</t>
         </is>
       </c>
       <c r="D155" s="19" t="inlineStr">
@@ -6951,10 +6972,10 @@
         </is>
       </c>
       <c r="E155" s="10" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
@@ -6970,29 +6991,29 @@
     <row r="156">
       <c r="A156" s="19" t="inlineStr">
         <is>
-          <t>GD1009938023608</t>
+          <t>IN99a5600da2fe8f23</t>
         </is>
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>AI-Machine Learning Engineer</t>
+          <t>Desktop Engineer Cum Business Analyst</t>
         </is>
       </c>
       <c r="C156" s="19" t="inlineStr">
         <is>
-          <t>V Support Solutions</t>
+          <t>Multiple zones Services LLP</t>
         </is>
       </c>
       <c r="D156" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E156" s="10" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
@@ -7001,24 +7022,24 @@
       </c>
       <c r="H156" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="19" t="inlineStr">
         <is>
-          <t>GD1010155316672</t>
+          <t>GD1010068823925</t>
         </is>
       </c>
       <c r="B157" s="19" t="inlineStr">
         <is>
-          <t>Senior ML Engineer (NLP/GenAI)</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="C157" s="19" t="inlineStr">
         <is>
-          <t>Vestas Wind Systems A/S</t>
+          <t>Everestek LLC</t>
         </is>
       </c>
       <c r="D157" s="19" t="inlineStr">
@@ -7027,10 +7048,10 @@
         </is>
       </c>
       <c r="E157" s="10" t="n">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
@@ -7046,29 +7067,29 @@
     <row r="158">
       <c r="A158" s="19" t="inlineStr">
         <is>
-          <t>GD1010177163435</t>
+          <t>LI4346596989</t>
         </is>
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>Guidewire developer | 6 to 12 years | PAN India</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>CapGemini SE</t>
+          <t>Rinovea</t>
         </is>
       </c>
       <c r="D158" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E158" s="10" t="n">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
@@ -7077,36 +7098,36 @@
       </c>
       <c r="H158" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="19" t="inlineStr">
         <is>
-          <t>GD1007999449903</t>
+          <t>LI4367151021</t>
         </is>
       </c>
       <c r="B159" s="19" t="inlineStr">
         <is>
-          <t>Fulltime React.js / Node js Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="C159" s="19" t="inlineStr">
         <is>
-          <t>Litost India Infotech Pvt Ltd</t>
+          <t>Sriggle</t>
         </is>
       </c>
       <c r="D159" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E159" s="10" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
@@ -7115,33 +7136,33 @@
       </c>
       <c r="H159" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="19" t="inlineStr">
         <is>
-          <t>GD1010182410096</t>
+          <t>LI4341525422</t>
         </is>
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst-Application Development-Data Visualization</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>ExlService Holdings, Inc.</t>
+          <t>TECHNIX TECHNOLOGY</t>
         </is>
       </c>
       <c r="D160" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E160" s="10" t="n">
-        <v>7</v>
+        <v>217</v>
       </c>
       <c r="F160" s="11" t="n">
         <v>0.9983</v>
@@ -7153,33 +7174,33 @@
       </c>
       <c r="H160" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="19" t="inlineStr">
         <is>
-          <t>GD1010189273543</t>
+          <t>LI4232601133</t>
         </is>
       </c>
       <c r="B161" s="19" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Backend Developer Trainee</t>
         </is>
       </c>
       <c r="C161" s="19" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>Gramik®</t>
         </is>
       </c>
       <c r="D161" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E161" s="10" t="n">
-        <v>3</v>
+        <v>365</v>
       </c>
       <c r="F161" s="11" t="n">
         <v>0.9983</v>
@@ -7191,24 +7212,24 @@
       </c>
       <c r="H161" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="19" t="inlineStr">
         <is>
-          <t>GD1010137931149</t>
+          <t>GD1010171807084</t>
         </is>
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data and Analytics Managing Consultant</t>
         </is>
       </c>
       <c r="C162" s="19" t="inlineStr">
         <is>
-          <t>BP p.l.c.</t>
+          <t>NTT DATA GROUP Corporation</t>
         </is>
       </c>
       <c r="D162" s="19" t="inlineStr">
@@ -7217,7 +7238,7 @@
         </is>
       </c>
       <c r="E162" s="10" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F162" s="11" t="n">
         <v>0.9983</v>
@@ -7236,29 +7257,29 @@
     <row r="163">
       <c r="A163" s="19" t="inlineStr">
         <is>
-          <t>GD1010189171534</t>
+          <t>LI4184468595</t>
         </is>
       </c>
       <c r="B163" s="19" t="inlineStr">
         <is>
-          <t>Business Analytics Analyst</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
         <is>
-          <t>Cigna Corporation</t>
+          <t>Jules AI</t>
         </is>
       </c>
       <c r="D163" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E163" s="10" t="n">
-        <v>3</v>
+        <v>365</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>0.9983</v>
+        <v>0.9982</v>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
@@ -7267,36 +7288,36 @@
       </c>
       <c r="H163" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="19" t="inlineStr">
         <is>
-          <t>GD1008999595896</t>
+          <t>LI4306131130</t>
         </is>
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>Sr. Angular Web Developer</t>
+          <t>NodeJS Developer</t>
         </is>
       </c>
       <c r="C164" s="19" t="inlineStr">
         <is>
-          <t>CONTUS TECH</t>
+          <t>DIAGNAL</t>
         </is>
       </c>
       <c r="D164" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E164" s="10" t="n">
-        <v>365</v>
+        <v>280</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>0.9983</v>
+        <v>0.9982</v>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
@@ -7305,24 +7326,24 @@
       </c>
       <c r="H164" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="19" t="inlineStr">
         <is>
-          <t>GD1009899665701</t>
+          <t>GD1009853609992</t>
         </is>
       </c>
       <c r="B165" s="19" t="inlineStr">
         <is>
-          <t>Business Analyst - Chennai</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C165" s="19" t="inlineStr">
         <is>
-          <t>Photon Infotech</t>
+          <t>Dantech Engenharia</t>
         </is>
       </c>
       <c r="D165" s="19" t="inlineStr">
@@ -7334,7 +7355,7 @@
         <v>128</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>0.9983</v>
+        <v>0.9982</v>
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
@@ -7350,17 +7371,17 @@
     <row r="166">
       <c r="A166" s="19" t="inlineStr">
         <is>
-          <t>GD1010156826705</t>
+          <t>GD1010175015614</t>
         </is>
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Frontend</t>
+          <t>Associate Technical Lead, Software Development</t>
         </is>
       </c>
       <c r="C166" s="19" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="D166" s="19" t="inlineStr">
@@ -7369,10 +7390,10 @@
         </is>
       </c>
       <c r="E166" s="10" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>0.9982</v>
+        <v>0.9981</v>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
@@ -7381,36 +7402,36 @@
       </c>
       <c r="H166" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="19" t="inlineStr">
         <is>
-          <t>GD1010165142277</t>
+          <t>IN9010d6f2dda92f09</t>
         </is>
       </c>
       <c r="B167" s="19" t="inlineStr">
         <is>
-          <t>Data Science and AI Analyst</t>
+          <t>Graphic / Multimedia Designer</t>
         </is>
       </c>
       <c r="C167" s="19" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Ecrystal Digital Technology</t>
         </is>
       </c>
       <c r="D167" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E167" s="10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>0.9982</v>
+        <v>0.9981</v>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
@@ -7419,33 +7440,33 @@
       </c>
       <c r="H167" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="19" t="inlineStr">
         <is>
-          <t>GD1010182468397</t>
+          <t>IN0411d4561b4da6d7</t>
         </is>
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>Tririga Business Analyst</t>
+          <t>Agentic AI Trainer</t>
         </is>
       </c>
       <c r="C168" s="19" t="inlineStr">
         <is>
-          <t>ISS A/S</t>
+          <t>Sikharthy</t>
         </is>
       </c>
       <c r="D168" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E168" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F168" s="11" t="n">
         <v>0.9981</v>
@@ -7464,26 +7485,26 @@
     <row r="169">
       <c r="A169" s="19" t="inlineStr">
         <is>
-          <t>GD1010188266576</t>
+          <t>IN3c656c218b571043</t>
         </is>
       </c>
       <c r="B169" s="19" t="inlineStr">
         <is>
-          <t>Data &amp; AI Lead Engineer</t>
+          <t>Internship HR Intern</t>
         </is>
       </c>
       <c r="C169" s="19" t="inlineStr">
         <is>
-          <t>NTT DATA GROUP Corporation</t>
+          <t>Tech Beam Design Private Limited</t>
         </is>
       </c>
       <c r="D169" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E169" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F169" s="11" t="n">
         <v>0.9981</v>
@@ -7502,26 +7523,26 @@
     <row r="170">
       <c r="A170" s="19" t="inlineStr">
         <is>
-          <t>GD1010116961866</t>
+          <t>INd72f224aca79bc7f</t>
         </is>
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - (Network Optimization)</t>
+          <t>Lorry driver 5 numbers with Heavy Driving Licence</t>
         </is>
       </c>
       <c r="C170" s="19" t="inlineStr">
         <is>
-          <t>A.P. Møller - Mærsk A/S</t>
+          <t>TAMIL SIDDHA HOSPITAL PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="D170" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E170" s="10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F170" s="11" t="n">
         <v>0.9981</v>
@@ -7533,36 +7554,36 @@
       </c>
       <c r="H170" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="19" t="inlineStr">
         <is>
-          <t>GD1010126807506</t>
+          <t>IN5d7407d8eedd3ba2</t>
         </is>
       </c>
       <c r="B171" s="19" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="C171" s="19" t="inlineStr">
         <is>
-          <t>Optum, Inc.</t>
+          <t>JFS Technologies PVT. Ltd</t>
         </is>
       </c>
       <c r="D171" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E171" s="10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>0.998</v>
+        <v>0.9981</v>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
@@ -7571,36 +7592,36 @@
       </c>
       <c r="H171" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="19" t="inlineStr">
         <is>
-          <t>GD1010182670988</t>
+          <t>LI4141152270</t>
         </is>
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>REACT JS  DEVELOPER</t>
         </is>
       </c>
       <c r="C172" s="19" t="inlineStr">
         <is>
-          <t>Siemens AG</t>
+          <t>Sequoia Applied Technologies</t>
         </is>
       </c>
       <c r="D172" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E172" s="10" t="n">
-        <v>7</v>
+        <v>365</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>0.998</v>
+        <v>0.9981</v>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
@@ -7609,24 +7630,24 @@
       </c>
       <c r="H172" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="19" t="inlineStr">
         <is>
-          <t>GD1010182639034</t>
+          <t>GD1010154948927</t>
         </is>
       </c>
       <c r="B173" s="19" t="inlineStr">
         <is>
-          <t>BI Engineer, Prime Data Engineering and Anaytics</t>
+          <t>Senior AWS Migration Engineer with Gen AI</t>
         </is>
       </c>
       <c r="C173" s="19" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D173" s="19" t="inlineStr">
@@ -7635,7 +7656,7 @@
         </is>
       </c>
       <c r="E173" s="10" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F173" s="11" t="n">
         <v>0.998</v>
@@ -7647,24 +7668,24 @@
       </c>
       <c r="H173" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="19" t="inlineStr">
         <is>
-          <t>GD1010173782303</t>
+          <t>GD1010177016034</t>
         </is>
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Workforce Analyst - Data Analytics</t>
         </is>
       </c>
       <c r="C174" s="19" t="inlineStr">
         <is>
-          <t>UBS AG</t>
+          <t xml:space="preserve">JPMorganChase </t>
         </is>
       </c>
       <c r="D174" s="19" t="inlineStr">
@@ -7673,7 +7694,7 @@
         </is>
       </c>
       <c r="E174" s="10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F174" s="11" t="n">
         <v>0.998</v>
@@ -7685,33 +7706,33 @@
       </c>
       <c r="H174" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="19" t="inlineStr">
         <is>
-          <t>GD1010186679920</t>
+          <t>LI4341580403</t>
         </is>
       </c>
       <c r="B175" s="19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, RAG and Agentic AI</t>
+          <t>Java Software Developer</t>
         </is>
       </c>
       <c r="C175" s="19" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Sns System Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D175" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E175" s="10" t="n">
-        <v>5</v>
+        <v>241</v>
       </c>
       <c r="F175" s="11" t="n">
         <v>0.998</v>
@@ -7723,24 +7744,24 @@
       </c>
       <c r="H175" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="19" t="inlineStr">
         <is>
-          <t>GD1009971205574</t>
+          <t>GD1010176883990</t>
         </is>
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>MLE(Machine Learning Engineer)</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="C176" s="19" t="inlineStr">
         <is>
-          <t>TWO95 International Inc.</t>
+          <t>Sai BioCare Pvt.Ltd</t>
         </is>
       </c>
       <c r="D176" s="19" t="inlineStr">
@@ -7749,7 +7770,7 @@
         </is>
       </c>
       <c r="E176" s="10" t="n">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="F176" s="11" t="n">
         <v>0.9979</v>
@@ -7761,33 +7782,33 @@
       </c>
       <c r="H176" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="19" t="inlineStr">
         <is>
-          <t>GD1010180686926</t>
+          <t>LI4356590646</t>
         </is>
       </c>
       <c r="B177" s="19" t="inlineStr">
         <is>
-          <t>AI Engineer – Physical AI &amp; Digital Twin Systems</t>
+          <t>MERN Stack Developer</t>
         </is>
       </c>
       <c r="C177" s="19" t="inlineStr">
         <is>
-          <t>Siemens AG</t>
+          <t>Dofin</t>
         </is>
       </c>
       <c r="D177" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E177" s="10" t="n">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="F177" s="11" t="n">
         <v>0.9979</v>
@@ -7799,24 +7820,24 @@
       </c>
       <c r="H177" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="19" t="inlineStr">
         <is>
-          <t>GD1010155398282</t>
+          <t>GD1010083845057</t>
         </is>
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – (gen AI)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="C178" s="19" t="inlineStr">
         <is>
-          <t>CodeCraft Technologies</t>
+          <t>Commdel Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D178" s="19" t="inlineStr">
@@ -7825,10 +7846,10 @@
         </is>
       </c>
       <c r="E178" s="10" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>0.9978</v>
+        <v>0.9979</v>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
@@ -7837,36 +7858,36 @@
       </c>
       <c r="H178" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="19" t="inlineStr">
         <is>
-          <t>GD1010163844877</t>
+          <t>INbb55aa7ad2d4fbcd</t>
         </is>
       </c>
       <c r="B179" s="19" t="inlineStr">
         <is>
-          <t>Procurement Data &amp; Analytics Analyst</t>
+          <t>MERN Stack Developer</t>
         </is>
       </c>
       <c r="C179" s="19" t="inlineStr">
         <is>
-          <t>Rolls-Royce Group plc</t>
+          <t>delphic</t>
         </is>
       </c>
       <c r="D179" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E179" s="10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>0.9978</v>
+        <v>0.9979</v>
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
@@ -7875,24 +7896,24 @@
       </c>
       <c r="H179" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="19" t="inlineStr">
         <is>
-          <t>LI4306126312</t>
+          <t>LI4352870573</t>
         </is>
       </c>
       <c r="B180" s="19" t="inlineStr">
         <is>
-          <t>Java API Developer</t>
+          <t>Software Tester / QA Engineer</t>
         </is>
       </c>
       <c r="C180" s="19" t="inlineStr">
         <is>
-          <t>Tetrasoft Inc.</t>
+          <t>LOVOJ</t>
         </is>
       </c>
       <c r="D180" s="19" t="inlineStr">
@@ -7901,10 +7922,10 @@
         </is>
       </c>
       <c r="E180" s="10" t="n">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>0.9978</v>
+        <v>0.9979</v>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
@@ -7920,29 +7941,29 @@
     <row r="181">
       <c r="A181" s="19" t="inlineStr">
         <is>
-          <t>GD1010145573372</t>
+          <t>LI4348870118</t>
         </is>
       </c>
       <c r="B181" s="19" t="inlineStr">
         <is>
-          <t>Sr Analyst, DACI Analytics</t>
+          <t>React Developer | Mumbai</t>
         </is>
       </c>
       <c r="C181" s="19" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>Tradelab Technologies</t>
         </is>
       </c>
       <c r="D181" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E181" s="10" t="n">
-        <v>41</v>
+        <v>212</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>0.9978</v>
+        <v>0.9979</v>
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
@@ -7951,36 +7972,36 @@
       </c>
       <c r="H181" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="19" t="inlineStr">
         <is>
-          <t>LI3625989522</t>
+          <t>GD1010158006345</t>
         </is>
       </c>
       <c r="B182" s="19" t="inlineStr">
         <is>
-          <t>Front End Engineer</t>
+          <t>Data Operations Analyst</t>
         </is>
       </c>
       <c r="C182" s="19" t="inlineStr">
         <is>
-          <t>Explorex Technologies, Inc. (YC S20)</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="D182" s="19" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Glassdoor</t>
         </is>
       </c>
       <c r="E182" s="10" t="n">
-        <v>365</v>
+        <v>32</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>0.9977</v>
+        <v>0.9979</v>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
@@ -7989,36 +8010,36 @@
       </c>
       <c r="H182" s="19" t="inlineStr">
         <is>
-          <t>employer_repost_count</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="19" t="inlineStr">
         <is>
-          <t>GD1010014774037</t>
+          <t>LI4361276299</t>
         </is>
       </c>
       <c r="B183" s="19" t="inlineStr">
         <is>
-          <t>AEM CMS/Frontend (Siliguri)</t>
+          <t>Full Stack Engineer - Python+React</t>
         </is>
       </c>
       <c r="C183" s="19" t="inlineStr">
         <is>
-          <t>Digitup B.V.</t>
+          <t>Creative Chaos</t>
         </is>
       </c>
       <c r="D183" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E183" s="10" t="n">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>0.9976</v>
+        <v>0.9979</v>
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
@@ -8027,24 +8048,24 @@
       </c>
       <c r="H183" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="19" t="inlineStr">
         <is>
-          <t>GD1010166417609</t>
+          <t>GD1010147194406</t>
         </is>
       </c>
       <c r="B184" s="19" t="inlineStr">
         <is>
-          <t>Front-end React Engineer</t>
+          <t>Engineer - Methods &amp; Tools (Data Analyst)</t>
         </is>
       </c>
       <c r="C184" s="19" t="inlineStr">
         <is>
-          <t>Quest Global Services Pte. Ltd.</t>
+          <t>Airbus S.A.S.</t>
         </is>
       </c>
       <c r="D184" s="19" t="inlineStr">
@@ -8053,10 +8074,10 @@
         </is>
       </c>
       <c r="E184" s="10" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>0.9976</v>
+        <v>0.9979</v>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
@@ -8072,17 +8093,17 @@
     <row r="185">
       <c r="A185" s="19" t="inlineStr">
         <is>
-          <t>GD1009983534560</t>
+          <t>GD1010171680953</t>
         </is>
       </c>
       <c r="B185" s="19" t="inlineStr">
         <is>
-          <t>python with AI/ML,pyspark,AWS</t>
+          <t>SAS Data analyst</t>
         </is>
       </c>
       <c r="C185" s="19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Limited</t>
+          <t>Citigroup Inc.</t>
         </is>
       </c>
       <c r="D185" s="19" t="inlineStr">
@@ -8091,10 +8112,10 @@
         </is>
       </c>
       <c r="E185" s="10" t="n">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>0.9976</v>
+        <v>0.9978</v>
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
@@ -8110,17 +8131,17 @@
     <row r="186">
       <c r="A186" s="19" t="inlineStr">
         <is>
-          <t>GD1010180872521</t>
+          <t>GD1010171626954</t>
         </is>
       </c>
       <c r="B186" s="19" t="inlineStr">
         <is>
-          <t>Analyst Operations</t>
+          <t>Business Development Analyst II</t>
         </is>
       </c>
       <c r="C186" s="19" t="inlineStr">
         <is>
-          <t>Medline Industries, Inc.</t>
+          <t>TE Connectivity Ltd.</t>
         </is>
       </c>
       <c r="D186" s="19" t="inlineStr">
@@ -8129,10 +8150,10 @@
         </is>
       </c>
       <c r="E186" s="10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>0.9976</v>
+        <v>0.9978</v>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
@@ -8141,24 +8162,24 @@
       </c>
       <c r="H186" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="19" t="inlineStr">
         <is>
-          <t>GD1009841577651</t>
+          <t>GD1010171045995</t>
         </is>
       </c>
       <c r="B187" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineering Analyst</t>
         </is>
       </c>
       <c r="C187" s="19" t="inlineStr">
         <is>
-          <t>Magic Infomedia</t>
+          <t>Optum, Inc.</t>
         </is>
       </c>
       <c r="D187" s="19" t="inlineStr">
@@ -8167,10 +8188,10 @@
         </is>
       </c>
       <c r="E187" s="10" t="n">
-        <v>128</v>
+        <v>19</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9978</v>
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
@@ -8179,36 +8200,36 @@
       </c>
       <c r="H187" s="19" t="inlineStr">
         <is>
-          <t>employer_repost_count</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="19" t="inlineStr">
         <is>
-          <t>GD1005900414928</t>
+          <t>IN020038210ae0debd</t>
         </is>
       </c>
       <c r="B188" s="19" t="inlineStr">
         <is>
-          <t>WEB DEVELOPER (Urgent Hiring)</t>
+          <t>Angular Full Stack Developer</t>
         </is>
       </c>
       <c r="C188" s="19" t="inlineStr">
         <is>
-          <t>WebPreneurs Pvt Ltd</t>
+          <t>Voicedots Infotech</t>
         </is>
       </c>
       <c r="D188" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E188" s="10" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9977</v>
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
@@ -8217,36 +8238,36 @@
       </c>
       <c r="H188" s="19" t="inlineStr">
         <is>
-          <t>employer_repost_count</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="19" t="inlineStr">
         <is>
-          <t>GD1010083845057</t>
+          <t>INbbdf125475f26528</t>
         </is>
       </c>
       <c r="B189" s="19" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C189" s="19" t="inlineStr">
         <is>
-          <t>Commdel Pvt. Ltd.</t>
+          <t>Fundtec Service LLP</t>
         </is>
       </c>
       <c r="D189" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E189" s="10" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>0.9973</v>
+        <v>0.9977</v>
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
@@ -8255,36 +8276,36 @@
       </c>
       <c r="H189" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="19" t="inlineStr">
         <is>
-          <t>GD1010047580920</t>
+          <t>IN16c0e2b616794219</t>
         </is>
       </c>
       <c r="B190" s="19" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Junior Backend Engineer</t>
         </is>
       </c>
       <c r="C190" s="19" t="inlineStr">
         <is>
-          <t>Gitakshmi Technologies Private Ltd.</t>
+          <t>Airavad Web Solutions</t>
         </is>
       </c>
       <c r="D190" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E190" s="10" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>0.9973</v>
+        <v>0.9977</v>
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
@@ -8293,36 +8314,36 @@
       </c>
       <c r="H190" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="19" t="inlineStr">
         <is>
-          <t>GD1010173801570</t>
+          <t>LI4078492078</t>
         </is>
       </c>
       <c r="B191" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Jr. Web Developer (PHP)</t>
         </is>
       </c>
       <c r="C191" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubi Electronics </t>
+          <t>Apex Tigre</t>
         </is>
       </c>
       <c r="D191" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E191" s="10" t="n">
-        <v>17</v>
+        <v>365</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>0.9973</v>
+        <v>0.9977</v>
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
@@ -8331,36 +8352,36 @@
       </c>
       <c r="H191" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="19" t="inlineStr">
         <is>
-          <t>GD1007764716710</t>
+          <t>LI4306114564</t>
         </is>
       </c>
       <c r="B192" s="19" t="inlineStr">
         <is>
-          <t>HTML 5, CSS3 &amp; bootstrap + js &amp; jquery developer</t>
+          <t>Software Development Engineer - Node.js/MongoDB</t>
         </is>
       </c>
       <c r="C192" s="19" t="inlineStr">
         <is>
-          <t>PrimaThink Technologies Private Limited</t>
+          <t>FlixStock</t>
         </is>
       </c>
       <c r="D192" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E192" s="10" t="n">
-        <v>133</v>
+        <v>280</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9977</v>
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
@@ -8369,36 +8390,36 @@
       </c>
       <c r="H192" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="19" t="inlineStr">
         <is>
-          <t>GD1008204441965</t>
+          <t>INc95aa76c832a6051</t>
         </is>
       </c>
       <c r="B193" s="19" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>AI/ML Engineer / Python</t>
         </is>
       </c>
       <c r="C193" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chiplogic Technologies Pvt Ltd </t>
+          <t>delphic</t>
         </is>
       </c>
       <c r="D193" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E193" s="10" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9977</v>
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
@@ -8407,24 +8428,24 @@
       </c>
       <c r="H193" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="19" t="inlineStr">
         <is>
-          <t>GD1010177066870</t>
+          <t>GD1010189376313</t>
         </is>
       </c>
       <c r="B194" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr Software Engineer (Frontend)</t>
         </is>
       </c>
       <c r="C194" s="19" t="inlineStr">
         <is>
-          <t>ExlService Holdings, Inc.</t>
+          <t>Siemens Healthcare GmbH</t>
         </is>
       </c>
       <c r="D194" s="19" t="inlineStr">
@@ -8433,10 +8454,10 @@
         </is>
       </c>
       <c r="E194" s="10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9976</v>
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
@@ -8452,17 +8473,17 @@
     <row r="195">
       <c r="A195" s="19" t="inlineStr">
         <is>
-          <t>GD1010173324197</t>
+          <t>GD1010189703338</t>
         </is>
       </c>
       <c r="B195" s="19" t="inlineStr">
         <is>
-          <t>Workday Reporting Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="C195" s="19" t="inlineStr">
         <is>
-          <t>Technology Next</t>
+          <t>IDC Research, Inc.</t>
         </is>
       </c>
       <c r="D195" s="19" t="inlineStr">
@@ -8471,10 +8492,10 @@
         </is>
       </c>
       <c r="E195" s="10" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9976</v>
       </c>
       <c r="G195" s="8" t="inlineStr">
         <is>
@@ -8483,24 +8504,24 @@
       </c>
       <c r="H195" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="19" t="inlineStr">
         <is>
-          <t>GD1010189207361</t>
+          <t>GD1008713225915</t>
         </is>
       </c>
       <c r="B196" s="19" t="inlineStr">
         <is>
-          <t>Engr III Cslt-Data Science</t>
+          <t>Web &amp; Mobile Developer</t>
         </is>
       </c>
       <c r="C196" s="19" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc.</t>
+          <t>Harness Digitech Private Limited</t>
         </is>
       </c>
       <c r="D196" s="19" t="inlineStr">
@@ -8509,10 +8530,10 @@
         </is>
       </c>
       <c r="E196" s="10" t="n">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9976</v>
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
@@ -8528,29 +8549,29 @@
     <row r="197">
       <c r="A197" s="19" t="inlineStr">
         <is>
-          <t>GD1008242226212</t>
+          <t>LI4264833835</t>
         </is>
       </c>
       <c r="B197" s="19" t="inlineStr">
         <is>
-          <t>React Js Developer</t>
+          <t>Web Development Trainer Pune Centre</t>
         </is>
       </c>
       <c r="C197" s="19" t="inlineStr">
         <is>
-          <t>Kanmalai Technologies Pvt Ltd</t>
+          <t>Bright Future</t>
         </is>
       </c>
       <c r="D197" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E197" s="10" t="n">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9976</v>
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
@@ -8559,36 +8580,36 @@
       </c>
       <c r="H197" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="19" t="inlineStr">
         <is>
-          <t>GD1008730016489</t>
+          <t>INdf7eb5ae43d41609</t>
         </is>
       </c>
       <c r="B198" s="19" t="inlineStr">
         <is>
-          <t>React.Js Developer</t>
+          <t>Executive IT - SQL Query Developer</t>
         </is>
       </c>
       <c r="C198" s="19" t="inlineStr">
         <is>
-          <t>Rentech Digital</t>
+          <t>Vitamed Logistics Private Limited</t>
         </is>
       </c>
       <c r="D198" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E198" s="10" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9976</v>
       </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
@@ -8597,24 +8618,24 @@
       </c>
       <c r="H198" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="19" t="inlineStr">
         <is>
-          <t>GD1010177066861</t>
+          <t>GD1010189703339</t>
         </is>
       </c>
       <c r="B199" s="19" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C199" s="19" t="inlineStr">
         <is>
-          <t>ExlService Holdings, Inc.</t>
+          <t>IDC Research, Inc.</t>
         </is>
       </c>
       <c r="D199" s="19" t="inlineStr">
@@ -8623,10 +8644,10 @@
         </is>
       </c>
       <c r="E199" s="10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9976</v>
       </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
@@ -8642,17 +8663,17 @@
     <row r="200">
       <c r="A200" s="19" t="inlineStr">
         <is>
-          <t>GD1009135352495</t>
+          <t>GD1010157388730</t>
         </is>
       </c>
       <c r="B200" s="19" t="inlineStr">
         <is>
-          <t>Data Research Analyst</t>
+          <t>Software Developer (1-5yrs)</t>
         </is>
       </c>
       <c r="C200" s="19" t="inlineStr">
         <is>
-          <t>Market Expertise Pty. Ltd.</t>
+          <t>danamojo Online Solutions Pvt. Ltd</t>
         </is>
       </c>
       <c r="D200" s="19" t="inlineStr">
@@ -8661,10 +8682,10 @@
         </is>
       </c>
       <c r="E200" s="10" t="n">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>0.9972</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
@@ -8680,17 +8701,17 @@
     <row r="201">
       <c r="A201" s="19" t="inlineStr">
         <is>
-          <t>GD1007838721358</t>
+          <t>GD1010189273529</t>
         </is>
       </c>
       <c r="B201" s="19" t="inlineStr">
         <is>
-          <t>UI Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C201" s="19" t="inlineStr">
         <is>
-          <t>Alleviate Technologies pvt ltd</t>
+          <t>Ecolab Inc.</t>
         </is>
       </c>
       <c r="D201" s="19" t="inlineStr">
@@ -8699,10 +8720,10 @@
         </is>
       </c>
       <c r="E201" s="10" t="n">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>0.9971</v>
+        <v>0.9974</v>
       </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
@@ -8711,24 +8732,24 @@
       </c>
       <c r="H201" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="19" t="inlineStr">
         <is>
-          <t>GD1008551659880</t>
+          <t>GD1010177029336</t>
         </is>
       </c>
       <c r="B202" s="19" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>Digital Software Engineer Senior Analyst - Web Development</t>
         </is>
       </c>
       <c r="C202" s="19" t="inlineStr">
         <is>
-          <t>Zimong Software Private Limited</t>
+          <t>Citigroup Inc.</t>
         </is>
       </c>
       <c r="D202" s="19" t="inlineStr">
@@ -8737,10 +8758,10 @@
         </is>
       </c>
       <c r="E202" s="10" t="n">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>0.9971</v>
+        <v>0.9974</v>
       </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
@@ -8749,36 +8770,36 @@
       </c>
       <c r="H202" s="19" t="inlineStr">
         <is>
-          <t>days_live</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="19" t="inlineStr">
         <is>
-          <t>GD1008687043240</t>
+          <t>INb5e54362fc6e7a2e</t>
         </is>
       </c>
       <c r="B203" s="19" t="inlineStr">
         <is>
-          <t>Web Designer Frontend / UX Developer</t>
+          <t>Business Analyst (Fresher / 1–2 Years Experience)</t>
         </is>
       </c>
       <c r="C203" s="19" t="inlineStr">
         <is>
-          <t>Akuna Technologies</t>
+          <t>DataGraphene Solutions</t>
         </is>
       </c>
       <c r="D203" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E203" s="10" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>0.9971</v>
+        <v>0.9974</v>
       </c>
       <c r="G203" s="8" t="inlineStr">
         <is>
@@ -8787,24 +8808,24 @@
       </c>
       <c r="H203" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="19" t="inlineStr">
         <is>
-          <t>GD1010067533464</t>
+          <t>GD1010142850457</t>
         </is>
       </c>
       <c r="B204" s="19" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Analyst</t>
+          <t>Applied ML Engineer</t>
         </is>
       </c>
       <c r="C204" s="19" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>Remotestar Ltd</t>
         </is>
       </c>
       <c r="D204" s="19" t="inlineStr">
@@ -8813,10 +8834,10 @@
         </is>
       </c>
       <c r="E204" s="10" t="n">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>0.9971</v>
+        <v>0.9974</v>
       </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
@@ -8832,29 +8853,29 @@
     <row r="205">
       <c r="A205" s="19" t="inlineStr">
         <is>
-          <t>GD1010147194406</t>
+          <t>LI4276144424</t>
         </is>
       </c>
       <c r="B205" s="19" t="inlineStr">
         <is>
-          <t>Engineer - Methods &amp; Tools (Data Analyst)</t>
+          <t>JavaScript Developer - Front-end</t>
         </is>
       </c>
       <c r="C205" s="19" t="inlineStr">
         <is>
-          <t>Airbus S.A.S.</t>
+          <t>Pippin Technologies India</t>
         </is>
       </c>
       <c r="D205" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E205" s="10" t="n">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="F205" s="11" t="n">
-        <v>0.9971</v>
+        <v>0.9974</v>
       </c>
       <c r="G205" s="8" t="inlineStr">
         <is>
@@ -8863,36 +8884,36 @@
       </c>
       <c r="H205" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="19" t="inlineStr">
         <is>
-          <t>GD1010168408727</t>
+          <t>IN5d17efedc9e91995</t>
         </is>
       </c>
       <c r="B206" s="19" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C206" s="19" t="inlineStr">
         <is>
-          <t>Ceiyone</t>
+          <t>TRAVEL DABBLE PRIVET LIMITED</t>
         </is>
       </c>
       <c r="D206" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E206" s="10" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>0.9971</v>
+        <v>0.9974</v>
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
@@ -8901,36 +8922,36 @@
       </c>
       <c r="H206" s="19" t="inlineStr">
         <is>
-          <t>listing_age_bucket</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="19" t="inlineStr">
         <is>
-          <t>GD1010076340201</t>
+          <t>LI4142489999</t>
         </is>
       </c>
       <c r="B207" s="19" t="inlineStr">
         <is>
-          <t>Sr Tableau Developer, Business Intelligence</t>
+          <t>JavaScript Developer</t>
         </is>
       </c>
       <c r="C207" s="19" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange, Inc.</t>
+          <t>Extension Technologies</t>
         </is>
       </c>
       <c r="D207" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E207" s="10" t="n">
-        <v>104</v>
+        <v>365</v>
       </c>
       <c r="F207" s="11" t="n">
-        <v>0.9971</v>
+        <v>0.9973</v>
       </c>
       <c r="G207" s="8" t="inlineStr">
         <is>
@@ -8939,36 +8960,36 @@
       </c>
       <c r="H207" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="19" t="inlineStr">
         <is>
-          <t>GD1009757118914</t>
+          <t>INce2438fb4e17d89c</t>
         </is>
       </c>
       <c r="B208" s="19" t="inlineStr">
         <is>
-          <t>Research Engineer</t>
+          <t>Technical Research Analyst</t>
         </is>
       </c>
       <c r="C208" s="19" t="inlineStr">
         <is>
-          <t>Niramai Health Analytix Pvt Ltd</t>
+          <t>Signal Expert Global LLP</t>
         </is>
       </c>
       <c r="D208" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E208" s="10" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>0.9971</v>
+        <v>0.9973</v>
       </c>
       <c r="G208" s="8" t="inlineStr">
         <is>
@@ -8977,36 +8998,36 @@
       </c>
       <c r="H208" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="19" t="inlineStr">
         <is>
-          <t>GD1007928568285</t>
+          <t>LI4060903567</t>
         </is>
       </c>
       <c r="B209" s="19" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C209" s="19" t="inlineStr">
         <is>
-          <t>Alps Web Solutions</t>
+          <t>InCred Money</t>
         </is>
       </c>
       <c r="D209" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E209" s="10" t="n">
-        <v>137</v>
+        <v>365</v>
       </c>
       <c r="F209" s="11" t="n">
-        <v>0.997</v>
+        <v>0.9973</v>
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
@@ -9015,36 +9036,36 @@
       </c>
       <c r="H209" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="19" t="inlineStr">
         <is>
-          <t>GD1007999853631</t>
+          <t>LI4306134088</t>
         </is>
       </c>
       <c r="B210" s="19" t="inlineStr">
         <is>
-          <t>Research Associate – Data Science</t>
+          <t>Frontend Developer (web Developer)</t>
         </is>
       </c>
       <c r="C210" s="19" t="inlineStr">
         <is>
-          <t>Recode Minds Pvt Ltd,</t>
+          <t>Kakatiya IT Solutions</t>
         </is>
       </c>
       <c r="D210" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E210" s="10" t="n">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>0.997</v>
+        <v>0.9973</v>
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
@@ -9060,17 +9081,17 @@
     <row r="211">
       <c r="A211" s="19" t="inlineStr">
         <is>
-          <t>GD1007236225631</t>
+          <t>GD1009992842022</t>
         </is>
       </c>
       <c r="B211" s="19" t="inlineStr">
         <is>
-          <t>SENIOR CONSULTANT - BI</t>
+          <t>Senior Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="C211" s="19" t="inlineStr">
         <is>
-          <t>The Hackett Group, Inc.</t>
+          <t>Jai Infoway</t>
         </is>
       </c>
       <c r="D211" s="19" t="inlineStr">
@@ -9079,10 +9100,10 @@
         </is>
       </c>
       <c r="E211" s="10" t="n">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="F211" s="11" t="n">
-        <v>0.997</v>
+        <v>0.9972</v>
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
@@ -9098,17 +9119,17 @@
     <row r="212">
       <c r="A212" s="19" t="inlineStr">
         <is>
-          <t>GD1009744142076</t>
+          <t>GD1010176176205</t>
         </is>
       </c>
       <c r="B212" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data &amp; Record Governance Analyst</t>
         </is>
       </c>
       <c r="C212" s="19" t="inlineStr">
         <is>
-          <t>Garuda Aerospace Private Limited</t>
+          <t>Barclays PLC</t>
         </is>
       </c>
       <c r="D212" s="19" t="inlineStr">
@@ -9117,10 +9138,10 @@
         </is>
       </c>
       <c r="E212" s="10" t="n">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9972</v>
       </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
@@ -9129,24 +9150,24 @@
       </c>
       <c r="H212" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="19" t="inlineStr">
         <is>
-          <t>GD1009957474447</t>
+          <t>GD1010160942923</t>
         </is>
       </c>
       <c r="B213" s="19" t="inlineStr">
         <is>
-          <t>Urgent React Developer</t>
+          <t>Quality Data Analytics Engineer</t>
         </is>
       </c>
       <c r="C213" s="19" t="inlineStr">
         <is>
-          <t>Esenceweb</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="D213" s="19" t="inlineStr">
@@ -9155,10 +9176,10 @@
         </is>
       </c>
       <c r="E213" s="10" t="n">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="F213" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9972</v>
       </c>
       <c r="G213" s="8" t="inlineStr">
         <is>
@@ -9167,36 +9188,36 @@
       </c>
       <c r="H213" s="19" t="inlineStr">
         <is>
-          <t>employer_repost_count</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="19" t="inlineStr">
         <is>
-          <t>GD1009697553308</t>
+          <t>LI4306132133</t>
         </is>
       </c>
       <c r="B214" s="19" t="inlineStr">
         <is>
-          <t>HTML Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C214" s="19" t="inlineStr">
         <is>
-          <t>Kush Infosystem Pvt. Ltd.,</t>
+          <t>MyInsuranceClub</t>
         </is>
       </c>
       <c r="D214" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E214" s="10" t="n">
-        <v>137</v>
+        <v>280</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9972</v>
       </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
@@ -9205,24 +9226,24 @@
       </c>
       <c r="H214" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="19" t="inlineStr">
         <is>
-          <t>GD1008402828250</t>
+          <t>GD1010054187264</t>
         </is>
       </c>
       <c r="B215" s="19" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C215" s="19" t="inlineStr">
         <is>
-          <t>Sciera Inc.</t>
+          <t>Indium Software Inc.</t>
         </is>
       </c>
       <c r="D215" s="19" t="inlineStr">
@@ -9231,10 +9252,10 @@
         </is>
       </c>
       <c r="E215" s="10" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F215" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9972</v>
       </c>
       <c r="G215" s="8" t="inlineStr">
         <is>
@@ -9250,29 +9271,29 @@
     <row r="216">
       <c r="A216" s="19" t="inlineStr">
         <is>
-          <t>GD1010180496962</t>
+          <t>LI4290659687</t>
         </is>
       </c>
       <c r="B216" s="19" t="inlineStr">
         <is>
-          <t>Data Analytics</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C216" s="19" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group AG</t>
+          <t>Quoqo</t>
         </is>
       </c>
       <c r="D216" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E216" s="10" t="n">
-        <v>10</v>
+        <v>316</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9972</v>
       </c>
       <c r="G216" s="8" t="inlineStr">
         <is>
@@ -9281,36 +9302,36 @@
       </c>
       <c r="H216" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="19" t="inlineStr">
         <is>
-          <t>GD1010175015614</t>
+          <t>INfd3bdcced70774be</t>
         </is>
       </c>
       <c r="B217" s="19" t="inlineStr">
         <is>
-          <t>Associate Technical Lead, Software Development</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C217" s="19" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>ReadyAssist Automobile Services</t>
         </is>
       </c>
       <c r="D217" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E217" s="10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F217" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9971</v>
       </c>
       <c r="G217" s="8" t="inlineStr">
         <is>
@@ -9326,17 +9347,17 @@
     <row r="218">
       <c r="A218" s="19" t="inlineStr">
         <is>
-          <t>GD1008123796798</t>
+          <t>GD1008687043240</t>
         </is>
       </c>
       <c r="B218" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Web Designer Frontend / UX Developer</t>
         </is>
       </c>
       <c r="C218" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Redinent Innovations Pvt Ltd.</t>
+          <t>Akuna Technologies</t>
         </is>
       </c>
       <c r="D218" s="19" t="inlineStr">
@@ -9348,7 +9369,7 @@
         <v>130</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9971</v>
       </c>
       <c r="G218" s="8" t="inlineStr">
         <is>
@@ -9364,17 +9385,17 @@
     <row r="219">
       <c r="A219" s="19" t="inlineStr">
         <is>
-          <t>GD1010005371754</t>
+          <t>GD1010180686926</t>
         </is>
       </c>
       <c r="B219" s="19" t="inlineStr">
         <is>
-          <t>AI/ML Developer (3–6 Yrs)</t>
+          <t>AI Engineer – Physical AI &amp; Digital Twin Systems</t>
         </is>
       </c>
       <c r="C219" s="19" t="inlineStr">
         <is>
-          <t>Seanergy Digital Inc.</t>
+          <t>Siemens AG</t>
         </is>
       </c>
       <c r="D219" s="19" t="inlineStr">
@@ -9383,10 +9404,10 @@
         </is>
       </c>
       <c r="E219" s="10" t="n">
-        <v>124</v>
+        <v>10</v>
       </c>
       <c r="F219" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9971</v>
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
@@ -9395,24 +9416,24 @@
       </c>
       <c r="H219" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="19" t="inlineStr">
         <is>
-          <t>GD1007909310817</t>
+          <t>GD1010172944279</t>
         </is>
       </c>
       <c r="B220" s="19" t="inlineStr">
         <is>
-          <t>FrontEnd Developer</t>
+          <t>Senior Marketing Technology Specialist (Employer of Record)</t>
         </is>
       </c>
       <c r="C220" s="19" t="inlineStr">
         <is>
-          <t>The Modern Dimension</t>
+          <t>Credit Acceptance Corporation</t>
         </is>
       </c>
       <c r="D220" s="19" t="inlineStr">
@@ -9421,10 +9442,10 @@
         </is>
       </c>
       <c r="E220" s="10" t="n">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>0.9969</v>
+        <v>0.9971</v>
       </c>
       <c r="G220" s="8" t="inlineStr">
         <is>
@@ -9440,29 +9461,29 @@
     <row r="221">
       <c r="A221" s="19" t="inlineStr">
         <is>
-          <t>GD1010063503283</t>
+          <t>LI4306132138</t>
         </is>
       </c>
       <c r="B221" s="19" t="inlineStr">
         <is>
-          <t>System Analyst</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="C221" s="19" t="inlineStr">
         <is>
-          <t>Avizva Solutions Pvt. Ltd.</t>
+          <t>Sveltetech Technologies</t>
         </is>
       </c>
       <c r="D221" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E221" s="10" t="n">
-        <v>116</v>
+        <v>280</v>
       </c>
       <c r="F221" s="11" t="n">
-        <v>0.9968</v>
+        <v>0.997</v>
       </c>
       <c r="G221" s="8" t="inlineStr">
         <is>
@@ -9471,36 +9492,36 @@
       </c>
       <c r="H221" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="19" t="inlineStr">
         <is>
-          <t>GD1009532125228</t>
+          <t>LI4306114570</t>
         </is>
       </c>
       <c r="B222" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst – Logistics Domain (Remote)</t>
+          <t>NodeJS Developer</t>
         </is>
       </c>
       <c r="C222" s="19" t="inlineStr">
         <is>
-          <t>Elevati Infotech Pvt Ltd</t>
+          <t>Unify Technologies</t>
         </is>
       </c>
       <c r="D222" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E222" s="10" t="n">
-        <v>129</v>
+        <v>280</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>0.9968</v>
+        <v>0.997</v>
       </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
@@ -9509,36 +9530,36 @@
       </c>
       <c r="H222" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="19" t="inlineStr">
         <is>
-          <t>GD1009081165420</t>
+          <t>LI4306126312</t>
         </is>
       </c>
       <c r="B223" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Java API Developer</t>
         </is>
       </c>
       <c r="C223" s="19" t="inlineStr">
         <is>
-          <t>SalesPointinc</t>
+          <t>Tetrasoft Inc.</t>
         </is>
       </c>
       <c r="D223" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E223" s="10" t="n">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="F223" s="11" t="n">
-        <v>0.9968</v>
+        <v>0.997</v>
       </c>
       <c r="G223" s="8" t="inlineStr">
         <is>
@@ -9547,24 +9568,24 @@
       </c>
       <c r="H223" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="19" t="inlineStr">
         <is>
-          <t>GD1010189273529</t>
+          <t>GD1010188320452</t>
         </is>
       </c>
       <c r="B224" s="19" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Frontend Developer (CMS Prismic)</t>
         </is>
       </c>
       <c r="C224" s="19" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>Genpact Limited</t>
         </is>
       </c>
       <c r="D224" s="19" t="inlineStr">
@@ -9573,10 +9594,10 @@
         </is>
       </c>
       <c r="E224" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>0.9968</v>
+        <v>0.997</v>
       </c>
       <c r="G224" s="8" t="inlineStr">
         <is>
@@ -9592,26 +9613,26 @@
     <row r="225">
       <c r="A225" s="19" t="inlineStr">
         <is>
-          <t>GD1009978345112</t>
+          <t>IN0f7e86f02bed3f17</t>
         </is>
       </c>
       <c r="B225" s="19" t="inlineStr">
         <is>
-          <t>AWS Bedrock AI Development Engineer</t>
+          <t>Video Editor</t>
         </is>
       </c>
       <c r="C225" s="19" t="inlineStr">
         <is>
-          <t>Cloudbyz Inc</t>
+          <t>Sage GFX Digital Solution</t>
         </is>
       </c>
       <c r="D225" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E225" s="10" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F225" s="11" t="n">
         <v>0.9968</v>
@@ -9623,24 +9644,24 @@
       </c>
       <c r="H225" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="19" t="inlineStr">
         <is>
-          <t>GD1006416784372</t>
+          <t>GD1009697553308</t>
         </is>
       </c>
       <c r="B226" s="19" t="inlineStr">
         <is>
-          <t>React JS Developer</t>
+          <t>HTML Developer</t>
         </is>
       </c>
       <c r="C226" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Technoarch Softwares </t>
+          <t>Kush Infosystem Pvt. Ltd.,</t>
         </is>
       </c>
       <c r="D226" s="19" t="inlineStr">
@@ -9668,7 +9689,7 @@
     <row r="227">
       <c r="A227" s="19" t="inlineStr">
         <is>
-          <t>LI4290659687</t>
+          <t>IN6c655c6cd7e6b784</t>
         </is>
       </c>
       <c r="B227" s="19" t="inlineStr">
@@ -9678,16 +9699,16 @@
       </c>
       <c r="C227" s="19" t="inlineStr">
         <is>
-          <t>Quoqo</t>
+          <t>Fundtec</t>
         </is>
       </c>
       <c r="D227" s="19" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E227" s="10" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="F227" s="11" t="n">
         <v>0.9968</v>
@@ -9699,24 +9720,24 @@
       </c>
       <c r="H227" s="19" t="inlineStr">
         <is>
-          <t>employer_repost_count</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="19" t="inlineStr">
         <is>
-          <t>GD1010015282838</t>
+          <t>GD1006034255929</t>
         </is>
       </c>
       <c r="B228" s="19" t="inlineStr">
         <is>
-          <t>GenAI engineer</t>
+          <t>Front End Developer</t>
         </is>
       </c>
       <c r="C228" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">HNM Solutions </t>
+          <t>TraveloPro</t>
         </is>
       </c>
       <c r="D228" s="19" t="inlineStr">
@@ -9725,7 +9746,7 @@
         </is>
       </c>
       <c r="E228" s="10" t="n">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="F228" s="11" t="n">
         <v>0.9967</v>
@@ -9744,26 +9765,26 @@
     <row r="229">
       <c r="A229" s="19" t="inlineStr">
         <is>
-          <t>GD1010028316025</t>
+          <t>LI4306122390</t>
         </is>
       </c>
       <c r="B229" s="19" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Advanced Machine Learning</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="C229" s="19" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>REDVision Technologies</t>
         </is>
       </c>
       <c r="D229" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E229" s="10" t="n">
-        <v>122</v>
+        <v>280</v>
       </c>
       <c r="F229" s="11" t="n">
         <v>0.9967</v>
@@ -9775,24 +9796,24 @@
       </c>
       <c r="H229" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="19" t="inlineStr">
         <is>
-          <t>GD1008457097003</t>
+          <t>GD1010186703724</t>
         </is>
       </c>
       <c r="B230" s="19" t="inlineStr">
         <is>
-          <t>UI Developer</t>
+          <t>Sr. Software Platform Engineer II</t>
         </is>
       </c>
       <c r="C230" s="19" t="inlineStr">
         <is>
-          <t>Aeon Logiciel</t>
+          <t>MetLife, Inc.</t>
         </is>
       </c>
       <c r="D230" s="19" t="inlineStr">
@@ -9801,7 +9822,7 @@
         </is>
       </c>
       <c r="E230" s="10" t="n">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="F230" s="11" t="n">
         <v>0.9967</v>
@@ -9813,24 +9834,24 @@
       </c>
       <c r="H230" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="19" t="inlineStr">
         <is>
-          <t>GD1010061778763</t>
+          <t>GD1010029238562</t>
         </is>
       </c>
       <c r="B231" s="19" t="inlineStr">
         <is>
-          <t>AI Engineer, India, 2-3 years</t>
+          <t>Hiring For Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C231" s="19" t="inlineStr">
         <is>
-          <t>ExlService Holdings, Inc.</t>
+          <t>BSRI Solutions Pvt Ltd</t>
         </is>
       </c>
       <c r="D231" s="19" t="inlineStr">
@@ -9839,7 +9860,7 @@
         </is>
       </c>
       <c r="E231" s="10" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F231" s="11" t="n">
         <v>0.9967</v>
@@ -9858,17 +9879,17 @@
     <row r="232">
       <c r="A232" s="19" t="inlineStr">
         <is>
-          <t>GD1010029357591</t>
+          <t>GD1010182468397</t>
         </is>
       </c>
       <c r="B232" s="19" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I</t>
+          <t>Tririga Business Analyst</t>
         </is>
       </c>
       <c r="C232" s="19" t="inlineStr">
         <is>
-          <t>Teleperformance SE</t>
+          <t>ISS A/S</t>
         </is>
       </c>
       <c r="D232" s="19" t="inlineStr">
@@ -9877,7 +9898,7 @@
         </is>
       </c>
       <c r="E232" s="10" t="n">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="F232" s="11" t="n">
         <v>0.9967</v>
@@ -9889,24 +9910,24 @@
       </c>
       <c r="H232" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="19" t="inlineStr">
         <is>
-          <t>GD1010178394464</t>
+          <t>GD1010176475069</t>
         </is>
       </c>
       <c r="B233" s="19" t="inlineStr">
         <is>
-          <t>Associate AI Data Engineer</t>
+          <t>Senior React Frontend Developer - 100% Remote</t>
         </is>
       </c>
       <c r="C233" s="19" t="inlineStr">
         <is>
-          <t>ExlService Holdings, Inc.</t>
+          <t>VGreenTEK</t>
         </is>
       </c>
       <c r="D233" s="19" t="inlineStr">
@@ -9915,7 +9936,7 @@
         </is>
       </c>
       <c r="E233" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F233" s="11" t="n">
         <v>0.9967</v>
@@ -9927,36 +9948,36 @@
       </c>
       <c r="H233" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="19" t="inlineStr">
         <is>
-          <t>GD1009183009766</t>
+          <t>IN392bfff87e7a7492</t>
         </is>
       </c>
       <c r="B234" s="19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Frontend</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C234" s="19" t="inlineStr">
         <is>
-          <t>VComply, Inc.</t>
+          <t>NKP Pharma Pvt Ltd Changodar</t>
         </is>
       </c>
       <c r="D234" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E234" s="10" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>0.9967</v>
+        <v>0.9966</v>
       </c>
       <c r="G234" s="8" t="inlineStr">
         <is>
@@ -9965,24 +9986,24 @@
       </c>
       <c r="H234" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="19" t="inlineStr">
         <is>
-          <t>GD1010178394554</t>
+          <t>GD1009989921449</t>
         </is>
       </c>
       <c r="B235" s="19" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="C235" s="19" t="inlineStr">
         <is>
-          <t>ExlService Holdings, Inc.</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="D235" s="19" t="inlineStr">
@@ -9991,10 +10012,10 @@
         </is>
       </c>
       <c r="E235" s="10" t="n">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="F235" s="11" t="n">
-        <v>0.9967</v>
+        <v>0.9966</v>
       </c>
       <c r="G235" s="8" t="inlineStr">
         <is>
@@ -10003,24 +10024,24 @@
       </c>
       <c r="H235" s="19" t="inlineStr">
         <is>
-          <t>salary_range_ratio</t>
+          <t>description_length_words</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="19" t="inlineStr">
         <is>
-          <t>GD1009943593992</t>
+          <t>GD1010188213677</t>
         </is>
       </c>
       <c r="B236" s="19" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software/Platform Engineer I</t>
         </is>
       </c>
       <c r="C236" s="19" t="inlineStr">
         <is>
-          <t>Avaamo, Inc</t>
+          <t>MetLife, Inc.</t>
         </is>
       </c>
       <c r="D236" s="19" t="inlineStr">
@@ -10029,10 +10050,10 @@
         </is>
       </c>
       <c r="E236" s="10" t="n">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>0.9967</v>
+        <v>0.9966</v>
       </c>
       <c r="G236" s="8" t="inlineStr">
         <is>
@@ -10041,33 +10062,33 @@
       </c>
       <c r="H236" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="19" t="inlineStr">
         <is>
-          <t>GD1010026037431</t>
+          <t>IN506ac0007375e8ed</t>
         </is>
       </c>
       <c r="B237" s="19" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C237" s="19" t="inlineStr">
         <is>
-          <t>Actoserba Active Wholesale Private Limited.</t>
+          <t>Need82 forex and travels private limited</t>
         </is>
       </c>
       <c r="D237" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E237" s="10" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="F237" s="11" t="n">
         <v>0.9966</v>
@@ -10079,24 +10100,24 @@
       </c>
       <c r="H237" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="19" t="inlineStr">
         <is>
-          <t>GD1010000857705</t>
+          <t>GD1010179410869</t>
         </is>
       </c>
       <c r="B238" s="19" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C238" s="19" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="D238" s="19" t="inlineStr">
@@ -10105,10 +10126,10 @@
         </is>
       </c>
       <c r="E238" s="10" t="n">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>0.9966</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G238" s="8" t="inlineStr">
         <is>
@@ -10117,24 +10138,24 @@
       </c>
       <c r="H238" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="19" t="inlineStr">
         <is>
-          <t>GD1010142850457</t>
+          <t>GD1010005722510</t>
         </is>
       </c>
       <c r="B239" s="19" t="inlineStr">
         <is>
-          <t>Applied ML Engineer</t>
+          <t>AI integration Engineer</t>
         </is>
       </c>
       <c r="C239" s="19" t="inlineStr">
         <is>
-          <t>Remotestar Ltd</t>
+          <t>Touchworld technology</t>
         </is>
       </c>
       <c r="D239" s="19" t="inlineStr">
@@ -10143,10 +10164,10 @@
         </is>
       </c>
       <c r="E239" s="10" t="n">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="F239" s="11" t="n">
-        <v>0.9966</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G239" s="8" t="inlineStr">
         <is>
@@ -10162,17 +10183,17 @@
     <row r="240">
       <c r="A240" s="19" t="inlineStr">
         <is>
-          <t>GD1009606922304</t>
+          <t>GD1010167234493</t>
         </is>
       </c>
       <c r="B240" s="19" t="inlineStr">
         <is>
-          <t>React.js Developer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="C240" s="19" t="inlineStr">
         <is>
-          <t>HashStudioz Technologies Pvt Ltd</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="D240" s="19" t="inlineStr">
@@ -10181,10 +10202,10 @@
         </is>
       </c>
       <c r="E240" s="10" t="n">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>0.9966</v>
+        <v>0.9964</v>
       </c>
       <c r="G240" s="8" t="inlineStr">
         <is>
@@ -10200,17 +10221,17 @@
     <row r="241">
       <c r="A241" s="19" t="inlineStr">
         <is>
-          <t>GD1008833461339</t>
+          <t>GD1010189171534</t>
         </is>
       </c>
       <c r="B241" s="19" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Business Analytics Analyst</t>
         </is>
       </c>
       <c r="C241" s="19" t="inlineStr">
         <is>
-          <t>TYASuite Software Solutions Private Limited</t>
+          <t>Cigna Corporation</t>
         </is>
       </c>
       <c r="D241" s="19" t="inlineStr">
@@ -10219,10 +10240,10 @@
         </is>
       </c>
       <c r="E241" s="10" t="n">
-        <v>130</v>
+        <v>3</v>
       </c>
       <c r="F241" s="11" t="n">
-        <v>0.9966</v>
+        <v>0.9964</v>
       </c>
       <c r="G241" s="8" t="inlineStr">
         <is>
@@ -10231,36 +10252,36 @@
       </c>
       <c r="H241" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="19" t="inlineStr">
         <is>
-          <t>INd72f224aca79bc7f</t>
+          <t>GD1010184544999</t>
         </is>
       </c>
       <c r="B242" s="19" t="inlineStr">
         <is>
-          <t>Lorry driver 5 numbers with Heavy Driving Licence</t>
+          <t>Contractor - Data Science &amp; AI</t>
         </is>
       </c>
       <c r="C242" s="19" t="inlineStr">
         <is>
-          <t>TAMIL SIDDHA HOSPITAL PRIVATE LIMITED</t>
+          <t>YASH Technologies, Inc.</t>
         </is>
       </c>
       <c r="D242" s="19" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Glassdoor</t>
         </is>
       </c>
       <c r="E242" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9964</v>
       </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
@@ -10276,17 +10297,17 @@
     <row r="243">
       <c r="A243" s="19" t="inlineStr">
         <is>
-          <t>GD1009900015966</t>
+          <t>GD1010180718556</t>
         </is>
       </c>
       <c r="B243" s="19" t="inlineStr">
         <is>
-          <t>Senior Staff Software Engineer</t>
+          <t>Data &amp; Analytics Analyst</t>
         </is>
       </c>
       <c r="C243" s="19" t="inlineStr">
         <is>
-          <t>Epsilon Data Management, LLC.</t>
+          <t>The Royal Bank of Scotland Group plc</t>
         </is>
       </c>
       <c r="D243" s="19" t="inlineStr">
@@ -10295,10 +10316,10 @@
         </is>
       </c>
       <c r="E243" s="10" t="n">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9964</v>
       </c>
       <c r="G243" s="8" t="inlineStr">
         <is>
@@ -10307,36 +10328,36 @@
       </c>
       <c r="H243" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="19" t="inlineStr">
         <is>
-          <t>GD1007415195803</t>
+          <t>LI4303974438</t>
         </is>
       </c>
       <c r="B244" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="C244" s="19" t="inlineStr">
         <is>
-          <t>Zessta Software Services Private Limited</t>
+          <t>GunjanApps Studios and Solutions LLP</t>
         </is>
       </c>
       <c r="D244" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E244" s="10" t="n">
-        <v>130</v>
+        <v>288</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9964</v>
       </c>
       <c r="G244" s="8" t="inlineStr">
         <is>
@@ -10345,24 +10366,24 @@
       </c>
       <c r="H244" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="19" t="inlineStr">
         <is>
-          <t>GD1010075318368</t>
+          <t>GD1008270450249</t>
         </is>
       </c>
       <c r="B245" s="19" t="inlineStr">
         <is>
-          <t>Senior Process Analyst- Six sigma - Bangalore</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C245" s="19" t="inlineStr">
         <is>
-          <t>Medi Assist Insurance TPA Pvt. Ltd.</t>
+          <t>Careervira</t>
         </is>
       </c>
       <c r="D245" s="19" t="inlineStr">
@@ -10371,10 +10392,10 @@
         </is>
       </c>
       <c r="E245" s="10" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9964</v>
       </c>
       <c r="G245" s="8" t="inlineStr">
         <is>
@@ -10383,36 +10404,36 @@
       </c>
       <c r="H245" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="19" t="inlineStr">
         <is>
-          <t>LI4276144424</t>
+          <t>GD1010182670988</t>
         </is>
       </c>
       <c r="B246" s="19" t="inlineStr">
         <is>
-          <t>JavaScript Developer - Front-end</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="C246" s="19" t="inlineStr">
         <is>
-          <t>Pippin Technologies India</t>
+          <t>Siemens AG</t>
         </is>
       </c>
       <c r="D246" s="19" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Glassdoor</t>
         </is>
       </c>
       <c r="E246" s="10" t="n">
-        <v>344</v>
+        <v>7</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9964</v>
       </c>
       <c r="G246" s="8" t="inlineStr">
         <is>
@@ -10421,24 +10442,24 @@
       </c>
       <c r="H246" s="19" t="inlineStr">
         <is>
-          <t>employer_repost_count</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="19" t="inlineStr">
         <is>
-          <t>GD1008584769095</t>
+          <t>GD1007838721358</t>
         </is>
       </c>
       <c r="B247" s="19" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>UI Developer</t>
         </is>
       </c>
       <c r="C247" s="19" t="inlineStr">
         <is>
-          <t>Pulse Associates Pvt. Ltd.</t>
+          <t>Alleviate Technologies pvt ltd</t>
         </is>
       </c>
       <c r="D247" s="19" t="inlineStr">
@@ -10447,7 +10468,7 @@
         </is>
       </c>
       <c r="E247" s="10" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F247" s="11" t="n">
         <v>0.9964</v>
@@ -10466,26 +10487,26 @@
     <row r="248">
       <c r="A248" s="19" t="inlineStr">
         <is>
-          <t>GD1009850362760</t>
+          <t>LI4306112554</t>
         </is>
       </c>
       <c r="B248" s="19" t="inlineStr">
         <is>
-          <t>AI Developer / Engineer</t>
+          <t>Fullstack Developer</t>
         </is>
       </c>
       <c r="C248" s="19" t="inlineStr">
         <is>
-          <t>Dimakh Consultants Pvt. Ltd</t>
+          <t>Propelius Technologies</t>
         </is>
       </c>
       <c r="D248" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E248" s="10" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F248" s="11" t="n">
         <v>0.9964</v>
@@ -10497,36 +10518,36 @@
       </c>
       <c r="H248" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>employer_repost_count</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="19" t="inlineStr">
         <is>
-          <t>GD1010013748241</t>
+          <t>IN603e29103eb87f60</t>
         </is>
       </c>
       <c r="B249" s="19" t="inlineStr">
         <is>
-          <t>Power BI (Data Analyst) Consultant</t>
+          <t>Full Stack Developer – AI Agent Integration</t>
         </is>
       </c>
       <c r="C249" s="19" t="inlineStr">
         <is>
-          <t>7N A/S</t>
+          <t>Weplacedyou</t>
         </is>
       </c>
       <c r="D249" s="19" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="E249" s="10" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>0.9964</v>
+        <v>0.9963</v>
       </c>
       <c r="G249" s="8" t="inlineStr">
         <is>
@@ -10535,24 +10556,24 @@
       </c>
       <c r="H249" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="19" t="inlineStr">
         <is>
-          <t>GD1009373319709</t>
+          <t>GD1010180341623</t>
         </is>
       </c>
       <c r="B250" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – II</t>
+          <t>Front-end Engineer - GPP/P2G</t>
         </is>
       </c>
       <c r="C250" s="19" t="inlineStr">
         <is>
-          <t>GrapheneAI</t>
+          <t xml:space="preserve">Finastra </t>
         </is>
       </c>
       <c r="D250" s="19" t="inlineStr">
@@ -10561,7 +10582,7 @@
         </is>
       </c>
       <c r="E250" s="10" t="n">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="F250" s="11" t="n">
         <v>0.9963</v>
@@ -10573,24 +10594,24 @@
       </c>
       <c r="H250" s="19" t="inlineStr">
         <is>
-          <t>description_length_words</t>
+          <t>salary_range_ratio</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="19" t="inlineStr">
         <is>
-          <t>GD1010030433890</t>
+          <t>GD1010168408727</t>
         </is>
       </c>
       <c r="B251" s="19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="C251" s="19" t="inlineStr">
         <is>
-          <t>Nexgile Technologies Pvt. Ltd</t>
+          <t>Ceiyone</t>
         </is>
       </c>
       <c r="D251" s="19" t="inlineStr">
@@ -10599,10 +10620,10 @@
         </is>
       </c>
       <c r="E251" s="10" t="n">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>0.9963</v>
+        <v>0.9962</v>
       </c>
       <c r="G251" s="8" t="inlineStr">
         <is>
